--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 днрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 днрсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\14,09,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822C56E6-6DDF-477B-9A90-1726C5EB84C8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE31EAC7-7F5E-4425-B3EA-3CD7E9A6F1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$117</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -740,7 +732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -763,8 +755,7 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -785,7 +776,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -6323,12 +6314,13 @@
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="21" width="7" customWidth="1"/>
-    <col min="22" max="22" width="7" style="23" customWidth="1"/>
+    <col min="22" max="22" width="7" style="22" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="34" width="6" customWidth="1"/>
     <col min="35" max="35" width="23.7109375" customWidth="1"/>
     <col min="36" max="37" width="7" customWidth="1"/>
-    <col min="38" max="51" width="3" customWidth="1"/>
+    <col min="38" max="38" width="6" customWidth="1"/>
+    <col min="39" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
@@ -6352,7 +6344,7 @@
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
-      <c r="U1" s="24">
+      <c r="U1" s="23">
         <v>0.5</v>
       </c>
       <c r="V1" s="9"/>
@@ -6773,7 +6765,10 @@
         <f>SUM(AK6:AK484)</f>
         <v>3912.92</v>
       </c>
-      <c r="AL5" s="9"/>
+      <c r="AL5" s="3">
+        <f>SUM(AL6:AL484)</f>
+        <v>2060.8523999999998</v>
+      </c>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
       <c r="AO5" s="9"/>
@@ -6847,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="4"/>
-      <c r="V6" s="22"/>
+      <c r="V6" s="9"/>
       <c r="W6" s="9">
         <f>(F6+O6+P6+S6)/Q6</f>
         <v>48.80572671257702</v>
@@ -6897,7 +6892,10 @@
         <f>G6*U6</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="9"/>
+      <c r="AL6" s="9">
+        <f>Q6*G6</f>
+        <v>0.55179999999999996</v>
+      </c>
       <c r="AM6" s="9"/>
       <c r="AN6" s="9"/>
       <c r="AO6" s="9"/>
@@ -6977,7 +6975,7 @@
         <f>ROUND(S7*$U$1,0)</f>
         <v>204</v>
       </c>
-      <c r="V7" s="22"/>
+      <c r="V7" s="9"/>
       <c r="W7" s="9">
         <f t="shared" ref="W7:W70" si="10">(F7+O7+P7+S7)/Q7</f>
         <v>15</v>
@@ -7025,7 +7023,10 @@
         <f t="shared" ref="AK7:AK70" si="12">G7*U7</f>
         <v>81.600000000000009</v>
       </c>
-      <c r="AL7" s="9"/>
+      <c r="AL7" s="9">
+        <f t="shared" ref="AL7:AL70" si="13">Q7*G7</f>
+        <v>23.840000000000003</v>
+      </c>
       <c r="AM7" s="9"/>
       <c r="AN7" s="9"/>
       <c r="AO7" s="9"/>
@@ -7101,7 +7102,7 @@
         <v>4</v>
       </c>
       <c r="U8" s="4"/>
-      <c r="V8" s="22"/>
+      <c r="V8" s="9"/>
       <c r="W8" s="9">
         <f t="shared" si="10"/>
         <v>15.513018024957633</v>
@@ -7151,7 +7152,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="9"/>
+      <c r="AL8" s="9">
+        <f t="shared" si="13"/>
+        <v>1.2982</v>
+      </c>
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
       <c r="AO8" s="9"/>
@@ -7232,7 +7236,7 @@
         <v>89</v>
       </c>
       <c r="U9" s="4"/>
-      <c r="V9" s="22"/>
+      <c r="V9" s="9"/>
       <c r="W9" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
@@ -7282,7 +7286,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL9" s="9"/>
+      <c r="AL9" s="9">
+        <f t="shared" si="13"/>
+        <v>8.9</v>
+      </c>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
       <c r="AO9" s="9"/>
@@ -7366,7 +7373,7 @@
         <f>ROUND(S10*$U$1,0)</f>
         <v>382</v>
       </c>
-      <c r="V10" s="22"/>
+      <c r="V10" s="9"/>
       <c r="W10" s="9">
         <f t="shared" si="10"/>
         <v>14.999011247776506</v>
@@ -7414,7 +7421,10 @@
         <f t="shared" si="12"/>
         <v>382</v>
       </c>
-      <c r="AL10" s="9"/>
+      <c r="AL10" s="9">
+        <f t="shared" si="13"/>
+        <v>208.34340000000003</v>
+      </c>
       <c r="AM10" s="9"/>
       <c r="AN10" s="9"/>
       <c r="AO10" s="9"/>
@@ -7486,7 +7496,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="4"/>
-      <c r="V11" s="22"/>
+      <c r="V11" s="9"/>
       <c r="W11" s="9">
         <f t="shared" si="10"/>
         <v>37.599384344766932</v>
@@ -7536,7 +7546,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="9"/>
+      <c r="AL11" s="9">
+        <f t="shared" si="13"/>
+        <v>2.274</v>
+      </c>
       <c r="AM11" s="9"/>
       <c r="AN11" s="9"/>
       <c r="AO11" s="9"/>
@@ -7613,10 +7626,10 @@
         <v>116</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" ref="U12:U13" si="13">ROUND(S12*$U$1,0)</f>
+        <f t="shared" ref="U12:U13" si="14">ROUND(S12*$U$1,0)</f>
         <v>116</v>
       </c>
-      <c r="V12" s="22"/>
+      <c r="V12" s="9"/>
       <c r="W12" s="9">
         <f t="shared" si="10"/>
         <v>14.995257526544204</v>
@@ -7664,7 +7677,10 @@
         <f t="shared" si="12"/>
         <v>116</v>
       </c>
-      <c r="AL12" s="9"/>
+      <c r="AL12" s="9">
+        <f t="shared" si="13"/>
+        <v>29.3096</v>
+      </c>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
       <c r="AO12" s="9"/>
@@ -7745,10 +7761,10 @@
         <v>127</v>
       </c>
       <c r="U13" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>127</v>
       </c>
-      <c r="V13" s="22"/>
+      <c r="V13" s="9"/>
       <c r="W13" s="9">
         <f t="shared" si="10"/>
         <v>15.003380817061247</v>
@@ -7796,7 +7812,10 @@
         <f t="shared" si="12"/>
         <v>127</v>
       </c>
-      <c r="AL13" s="9"/>
+      <c r="AL13" s="9">
+        <f t="shared" si="13"/>
+        <v>87.552800000000005</v>
+      </c>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
       <c r="AO13" s="9"/>
@@ -7872,7 +7891,7 @@
         <v>8</v>
       </c>
       <c r="U14" s="4"/>
-      <c r="V14" s="22"/>
+      <c r="V14" s="9"/>
       <c r="W14" s="9">
         <f t="shared" si="10"/>
         <v>15.666666666666666</v>
@@ -7922,7 +7941,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="9"/>
+      <c r="AL14" s="9">
+        <f t="shared" si="13"/>
+        <v>1.5</v>
+      </c>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
       <c r="AO14" s="9"/>
@@ -7999,7 +8021,7 @@
         <v>160</v>
       </c>
       <c r="U15" s="4"/>
-      <c r="V15" s="22"/>
+      <c r="V15" s="9"/>
       <c r="W15" s="9">
         <f t="shared" si="10"/>
         <v>14.992441700670206</v>
@@ -8047,7 +8069,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="9"/>
+      <c r="AL15" s="9">
+        <f t="shared" si="13"/>
+        <v>18.919599999999999</v>
+      </c>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
       <c r="AO15" s="9"/>
@@ -8126,7 +8151,7 @@
         <v>89</v>
       </c>
       <c r="U16" s="4"/>
-      <c r="V16" s="22"/>
+      <c r="V16" s="9"/>
       <c r="W16" s="9">
         <f t="shared" si="10"/>
         <v>14.999999999999998</v>
@@ -8176,7 +8201,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="9"/>
+      <c r="AL16" s="9">
+        <f t="shared" si="13"/>
+        <v>4.1500000000000004</v>
+      </c>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
       <c r="AO16" s="9"/>
@@ -8257,7 +8285,7 @@
         <f>ROUND(S17*$U$1,0)</f>
         <v>500</v>
       </c>
-      <c r="V17" s="22">
+      <c r="V17" s="9">
         <f>VLOOKUP(A17,[1]Sheet!$A:$S,19,0)</f>
         <v>1000</v>
       </c>
@@ -8310,7 +8338,10 @@
         <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="AL17" s="9"/>
+      <c r="AL17" s="9">
+        <f t="shared" si="13"/>
+        <v>66.960000000000008</v>
+      </c>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
       <c r="AO17" s="9"/>
@@ -8378,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="4"/>
-      <c r="V18" s="22"/>
+      <c r="V18" s="9"/>
       <c r="W18" s="9">
         <f t="shared" si="10"/>
         <v>-5</v>
@@ -8426,7 +8457,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="9"/>
+      <c r="AL18" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
       <c r="AO18" s="9"/>
@@ -8495,7 +8529,7 @@
         <v>67.917599999999993</v>
       </c>
       <c r="R19" s="4">
-        <f t="shared" ref="R19:R32" si="14">15*Q19-P19-O19-F19</f>
+        <f t="shared" ref="R19:R32" si="15">15*Q19-P19-O19-F19</f>
         <v>349.21399999999988</v>
       </c>
       <c r="S19" s="4">
@@ -8510,7 +8544,7 @@
         <f>ROUND(S19*$U$1,0)</f>
         <v>175</v>
       </c>
-      <c r="V19" s="22"/>
+      <c r="V19" s="9"/>
       <c r="W19" s="9">
         <f t="shared" si="10"/>
         <v>14.996849123054997</v>
@@ -8558,7 +8592,10 @@
         <f t="shared" si="12"/>
         <v>175</v>
       </c>
-      <c r="AL19" s="9"/>
+      <c r="AL19" s="9">
+        <f t="shared" si="13"/>
+        <v>67.917599999999993</v>
+      </c>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
       <c r="AO19" s="9"/>
@@ -8623,7 +8660,7 @@
         <v>4.3908000000000005</v>
       </c>
       <c r="R20" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29.791000000000007</v>
       </c>
       <c r="S20" s="4">
@@ -8635,7 +8672,7 @@
         <v>30</v>
       </c>
       <c r="U20" s="4"/>
-      <c r="V20" s="22"/>
+      <c r="V20" s="9"/>
       <c r="W20" s="9">
         <f t="shared" si="10"/>
         <v>15.047599526282225</v>
@@ -8685,7 +8722,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="9"/>
+      <c r="AL20" s="9">
+        <f t="shared" si="13"/>
+        <v>4.3908000000000005</v>
+      </c>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
       <c r="AO20" s="9"/>
@@ -8752,7 +8792,7 @@
         <v>55</v>
       </c>
       <c r="R21" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>58</v>
       </c>
       <c r="S21" s="4">
@@ -8764,7 +8804,7 @@
         <v>58</v>
       </c>
       <c r="U21" s="4"/>
-      <c r="V21" s="22"/>
+      <c r="V21" s="9"/>
       <c r="W21" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
@@ -8812,7 +8852,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="9"/>
+      <c r="AL21" s="9">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
       <c r="AO21" s="9"/>
@@ -8879,7 +8922,7 @@
         <v>53.6404</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>171.23000000000002</v>
       </c>
       <c r="S22" s="4">
@@ -8891,7 +8934,7 @@
         <v>171</v>
       </c>
       <c r="U22" s="4"/>
-      <c r="V22" s="22"/>
+      <c r="V22" s="9"/>
       <c r="W22" s="9">
         <f t="shared" si="10"/>
         <v>14.995712187082869</v>
@@ -8939,7 +8982,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="9"/>
+      <c r="AL22" s="9">
+        <f t="shared" si="13"/>
+        <v>53.6404</v>
+      </c>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
       <c r="AO22" s="9"/>
@@ -9018,7 +9064,7 @@
         <f>ROUND(S23*$U$1,0)</f>
         <v>225</v>
       </c>
-      <c r="V23" s="22"/>
+      <c r="V23" s="9"/>
       <c r="W23" s="9">
         <f t="shared" si="10"/>
         <v>8.9233576642335777</v>
@@ -9068,7 +9114,10 @@
         <f t="shared" si="12"/>
         <v>49.5</v>
       </c>
-      <c r="AL23" s="9"/>
+      <c r="AL23" s="9">
+        <f t="shared" si="13"/>
+        <v>24.111999999999998</v>
+      </c>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
       <c r="AO23" s="9"/>
@@ -9131,7 +9180,7 @@
         <v>3.3003999999999998</v>
       </c>
       <c r="R24" s="4">
-        <f t="shared" ref="R24" si="15">14*Q24-P24-O24-F24</f>
+        <f t="shared" ref="R24" si="16">14*Q24-P24-O24-F24</f>
         <v>29.601599999999998</v>
       </c>
       <c r="S24" s="4">
@@ -9143,7 +9192,7 @@
         <v>30</v>
       </c>
       <c r="U24" s="4"/>
-      <c r="V24" s="22"/>
+      <c r="V24" s="9"/>
       <c r="W24" s="9">
         <f t="shared" si="10"/>
         <v>14.120712640892014</v>
@@ -9191,7 +9240,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="9"/>
+      <c r="AL24" s="9">
+        <f t="shared" si="13"/>
+        <v>3.3003999999999998</v>
+      </c>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
       <c r="AO24" s="9"/>
@@ -9260,7 +9312,7 @@
         <v>87.558400000000006</v>
       </c>
       <c r="R25" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>431.37900000000019</v>
       </c>
       <c r="S25" s="4">
@@ -9272,10 +9324,10 @@
         <v>215</v>
       </c>
       <c r="U25" s="4">
-        <f t="shared" ref="U25:U26" si="16">ROUND(S25*$U$1,0)</f>
+        <f t="shared" ref="U25:U26" si="17">ROUND(S25*$U$1,0)</f>
         <v>216</v>
       </c>
-      <c r="V25" s="22"/>
+      <c r="V25" s="9"/>
       <c r="W25" s="9">
         <f t="shared" si="10"/>
         <v>14.99567146041956</v>
@@ -9323,7 +9375,10 @@
         <f t="shared" si="12"/>
         <v>216</v>
       </c>
-      <c r="AL25" s="9"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="13"/>
+        <v>87.558400000000006</v>
+      </c>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
       <c r="AO25" s="9"/>
@@ -9392,7 +9447,7 @@
         <v>93.6</v>
       </c>
       <c r="R26" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>669</v>
       </c>
       <c r="S26" s="4">
@@ -9404,10 +9459,10 @@
         <v>334</v>
       </c>
       <c r="U26" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>335</v>
       </c>
-      <c r="V26" s="22"/>
+      <c r="V26" s="9"/>
       <c r="W26" s="9">
         <f t="shared" si="10"/>
         <v>15.000000000000002</v>
@@ -9455,7 +9510,10 @@
         <f t="shared" si="12"/>
         <v>30.15</v>
       </c>
-      <c r="AL26" s="9"/>
+      <c r="AL26" s="9">
+        <f t="shared" si="13"/>
+        <v>8.4239999999999995</v>
+      </c>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
       <c r="AO26" s="9"/>
@@ -9520,7 +9578,7 @@
         <v>12.2</v>
       </c>
       <c r="R27" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="S27" s="4">
@@ -9532,7 +9590,7 @@
         <v>50</v>
       </c>
       <c r="U27" s="4"/>
-      <c r="V27" s="22">
+      <c r="V27" s="9">
         <f>VLOOKUP(A27,[1]Sheet!$A:$S,19,0)</f>
         <v>50</v>
       </c>
@@ -9583,7 +9641,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="9"/>
+      <c r="AL27" s="9">
+        <f t="shared" si="13"/>
+        <v>1.0979999999999999</v>
+      </c>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
       <c r="AO27" s="9"/>
@@ -9650,7 +9711,7 @@
         <v>8.4</v>
       </c>
       <c r="R28" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>25</v>
       </c>
       <c r="S28" s="4">
@@ -9662,7 +9723,7 @@
         <v>25</v>
       </c>
       <c r="U28" s="4"/>
-      <c r="V28" s="22"/>
+      <c r="V28" s="9"/>
       <c r="W28" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
@@ -9712,7 +9773,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL28" s="9"/>
+      <c r="AL28" s="9">
+        <f t="shared" si="13"/>
+        <v>1.26</v>
+      </c>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
       <c r="AO28" s="9"/>
@@ -9788,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="4"/>
-      <c r="V29" s="22"/>
+      <c r="V29" s="9"/>
       <c r="W29" s="9">
         <f t="shared" si="10"/>
         <v>15.386031326541849</v>
@@ -9836,7 +9900,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="9"/>
+      <c r="AL29" s="9">
+        <f t="shared" si="13"/>
+        <v>67.201800000000006</v>
+      </c>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9"/>
@@ -9912,7 +9979,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="4"/>
-      <c r="V30" s="22"/>
+      <c r="V30" s="9"/>
       <c r="W30" s="9">
         <f t="shared" si="10"/>
         <v>30.810810810810811</v>
@@ -9962,7 +10029,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL30" s="9"/>
+      <c r="AL30" s="9">
+        <f t="shared" si="13"/>
+        <v>2.9600000000000004</v>
+      </c>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9"/>
@@ -10029,7 +10099,7 @@
         <v>125.4</v>
       </c>
       <c r="R31" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>408</v>
       </c>
       <c r="S31" s="4">
@@ -10040,10 +10110,10 @@
         <v>500</v>
       </c>
       <c r="U31" s="4">
-        <f t="shared" ref="U31:U32" si="17">ROUND(S31*$U$1,0)</f>
+        <f t="shared" ref="U31:U32" si="18">ROUND(S31*$U$1,0)</f>
         <v>500</v>
       </c>
-      <c r="V31" s="22">
+      <c r="V31" s="9">
         <f>VLOOKUP(A31,[1]Sheet!$A:$S,19,0)</f>
         <v>1408</v>
       </c>
@@ -10094,7 +10164,10 @@
         <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="AL31" s="9"/>
+      <c r="AL31" s="9">
+        <f t="shared" si="13"/>
+        <v>50.160000000000004</v>
+      </c>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
       <c r="AO31" s="9"/>
@@ -10163,7 +10236,7 @@
         <v>149.19999999999999</v>
       </c>
       <c r="R32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1046.3319999999999</v>
       </c>
       <c r="S32" s="4">
@@ -10175,10 +10248,10 @@
         <v>523</v>
       </c>
       <c r="U32" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>523</v>
       </c>
-      <c r="V32" s="22"/>
+      <c r="V32" s="9"/>
       <c r="W32" s="9">
         <f t="shared" si="10"/>
         <v>14.997774798927615</v>
@@ -10228,7 +10301,10 @@
         <f t="shared" si="12"/>
         <v>209.20000000000002</v>
       </c>
-      <c r="AL32" s="9"/>
+      <c r="AL32" s="9">
+        <f t="shared" si="13"/>
+        <v>59.68</v>
+      </c>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
       <c r="AO32" s="9"/>
@@ -10300,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="4"/>
-      <c r="V33" s="22"/>
+      <c r="V33" s="9"/>
       <c r="W33" s="9">
         <f t="shared" si="10"/>
         <v>58.333333333333336</v>
@@ -10350,7 +10426,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="9"/>
+      <c r="AL33" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
       <c r="AO33" s="9"/>
@@ -10427,7 +10506,7 @@
         <v>117</v>
       </c>
       <c r="U34" s="4"/>
-      <c r="V34" s="22"/>
+      <c r="V34" s="9"/>
       <c r="W34" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
@@ -10475,7 +10554,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="9"/>
+      <c r="AL34" s="9">
+        <f t="shared" si="13"/>
+        <v>7.74</v>
+      </c>
       <c r="AM34" s="9"/>
       <c r="AN34" s="9"/>
       <c r="AO34" s="9"/>
@@ -10554,7 +10636,7 @@
         <v>46</v>
       </c>
       <c r="U35" s="4"/>
-      <c r="V35" s="22"/>
+      <c r="V35" s="9"/>
       <c r="W35" s="9">
         <f t="shared" si="10"/>
         <v>14.986116941750078</v>
@@ -10602,7 +10684,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="9"/>
+      <c r="AL35" s="9">
+        <f t="shared" si="13"/>
+        <v>27.155399999999997</v>
+      </c>
       <c r="AM35" s="9"/>
       <c r="AN35" s="9"/>
       <c r="AO35" s="9"/>
@@ -10676,7 +10761,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="4"/>
-      <c r="V36" s="22"/>
+      <c r="V36" s="9"/>
       <c r="W36" s="9">
         <f t="shared" si="10"/>
         <v>15.830296504886535</v>
@@ -10724,7 +10809,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="9"/>
+      <c r="AL36" s="9">
+        <f t="shared" si="13"/>
+        <v>9.6592000000000002</v>
+      </c>
       <c r="AM36" s="9"/>
       <c r="AN36" s="9"/>
       <c r="AO36" s="9"/>
@@ -10792,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="U37" s="4"/>
-      <c r="V37" s="22"/>
+      <c r="V37" s="9"/>
       <c r="W37" s="9" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
@@ -10840,7 +10928,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL37" s="9"/>
+      <c r="AL37" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM37" s="9"/>
       <c r="AN37" s="9"/>
       <c r="AO37" s="9"/>
@@ -10888,11 +10979,11 @@
         <v>78.2</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" ref="L38:L69" si="18">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="19">E38-K38</f>
         <v>-5.9920000000000044</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" ref="M38:M69" si="19">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="20">E38-N38</f>
         <v>72.207999999999998</v>
       </c>
       <c r="N38" s="9"/>
@@ -10901,7 +10992,7 @@
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="9">
-        <f t="shared" ref="Q38:Q69" si="20">M38/5</f>
+        <f t="shared" ref="Q38:Q69" si="21">M38/5</f>
         <v>14.441599999999999</v>
       </c>
       <c r="R38" s="4"/>
@@ -10914,13 +11005,13 @@
         <v>0</v>
       </c>
       <c r="U38" s="4"/>
-      <c r="V38" s="22"/>
+      <c r="V38" s="9"/>
       <c r="W38" s="9">
         <f t="shared" si="10"/>
         <v>15.116192111677377</v>
       </c>
       <c r="X38" s="9">
-        <f t="shared" ref="X38:X69" si="21">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="X38:X69" si="22">(F38+O38+P38)/Q38</f>
         <v>15.116192111677377</v>
       </c>
       <c r="Y38" s="9">
@@ -10962,7 +11053,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL38" s="9"/>
+      <c r="AL38" s="9">
+        <f t="shared" si="13"/>
+        <v>14.441599999999999</v>
+      </c>
       <c r="AM38" s="9"/>
       <c r="AN38" s="9"/>
       <c r="AO38" s="9"/>
@@ -11010,11 +11104,11 @@
         <v>205</v>
       </c>
       <c r="L39" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-11.219999999999999</v>
       </c>
       <c r="M39" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>153.48000000000002</v>
       </c>
       <c r="N39" s="9">
@@ -11027,7 +11121,7 @@
         <v>126</v>
       </c>
       <c r="Q39" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>30.696000000000005</v>
       </c>
       <c r="R39" s="4">
@@ -11043,13 +11137,13 @@
         <v>103</v>
       </c>
       <c r="U39" s="4"/>
-      <c r="V39" s="22"/>
+      <c r="V39" s="9"/>
       <c r="W39" s="9">
         <f t="shared" si="10"/>
         <v>15.01492051081574</v>
       </c>
       <c r="X39" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.65943445400052</v>
       </c>
       <c r="Y39" s="9">
@@ -11091,7 +11185,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL39" s="9"/>
+      <c r="AL39" s="9">
+        <f t="shared" si="13"/>
+        <v>30.696000000000005</v>
+      </c>
       <c r="AM39" s="9"/>
       <c r="AN39" s="9"/>
       <c r="AO39" s="9"/>
@@ -11133,11 +11230,11 @@
         <v>51</v>
       </c>
       <c r="L40" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-15</v>
       </c>
       <c r="M40" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N40" s="15">
@@ -11148,7 +11245,7 @@
       </c>
       <c r="P40" s="15"/>
       <c r="Q40" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R40" s="18"/>
@@ -11161,13 +11258,13 @@
         <v>0</v>
       </c>
       <c r="U40" s="4"/>
-      <c r="V40" s="22"/>
+      <c r="V40" s="9"/>
       <c r="W40" s="9" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X40" s="15" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y40" s="15">
@@ -11209,7 +11306,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL40" s="9"/>
+      <c r="AL40" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM40" s="9"/>
       <c r="AN40" s="9"/>
       <c r="AO40" s="9"/>
@@ -11257,11 +11357,11 @@
         <v>433</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-201</v>
       </c>
       <c r="M41" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>232</v>
       </c>
       <c r="N41" s="9"/>
@@ -11272,11 +11372,11 @@
         <v>193</v>
       </c>
       <c r="Q41" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>46.4</v>
       </c>
       <c r="R41" s="4">
-        <f t="shared" ref="R41:R46" si="22">15*Q41-P41-O41-F41</f>
+        <f t="shared" ref="R41:R46" si="23">15*Q41-P41-O41-F41</f>
         <v>224</v>
       </c>
       <c r="S41" s="4">
@@ -11291,7 +11391,7 @@
         <f>ROUND(S41*$U$1,0)</f>
         <v>150</v>
       </c>
-      <c r="V41" s="22">
+      <c r="V41" s="9">
         <f>VLOOKUP(A41,[1]Sheet!$A:$S,19,0)</f>
         <v>300</v>
       </c>
@@ -11300,7 +11400,7 @@
         <v>16.637931034482758</v>
       </c>
       <c r="X41" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.172413793103448</v>
       </c>
       <c r="Y41" s="9">
@@ -11344,7 +11444,10 @@
         <f t="shared" si="12"/>
         <v>45</v>
       </c>
-      <c r="AL41" s="9"/>
+      <c r="AL41" s="9">
+        <f t="shared" si="13"/>
+        <v>13.92</v>
+      </c>
       <c r="AM41" s="9"/>
       <c r="AN41" s="9"/>
       <c r="AO41" s="9"/>
@@ -11388,11 +11491,11 @@
         <v>49.021999999999998</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.132000000000005</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>50.154000000000003</v>
       </c>
       <c r="N42" s="9"/>
@@ -11401,11 +11504,11 @@
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.030800000000001</v>
       </c>
       <c r="R42" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>43.268000000000015</v>
       </c>
       <c r="S42" s="4">
@@ -11417,13 +11520,13 @@
         <v>43</v>
       </c>
       <c r="U42" s="4"/>
-      <c r="V42" s="22"/>
+      <c r="V42" s="9"/>
       <c r="W42" s="9">
         <f t="shared" si="10"/>
         <v>14.973282290545121</v>
       </c>
       <c r="X42" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.686485624277225</v>
       </c>
       <c r="Y42" s="9">
@@ -11467,7 +11570,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL42" s="9"/>
+      <c r="AL42" s="9">
+        <f t="shared" si="13"/>
+        <v>10.030800000000001</v>
+      </c>
       <c r="AM42" s="9"/>
       <c r="AN42" s="9"/>
       <c r="AO42" s="9"/>
@@ -11515,11 +11621,11 @@
         <v>33.533000000000001</v>
       </c>
       <c r="L43" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.7999999999996703E-2</v>
       </c>
       <c r="M43" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.0379999999999967</v>
       </c>
       <c r="N43" s="9">
@@ -11530,7 +11636,7 @@
       </c>
       <c r="P43" s="9"/>
       <c r="Q43" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.60759999999999936</v>
       </c>
       <c r="R43" s="4"/>
@@ -11543,13 +11649,13 @@
         <v>0</v>
       </c>
       <c r="U43" s="4"/>
-      <c r="V43" s="22"/>
+      <c r="V43" s="9"/>
       <c r="W43" s="9">
         <f t="shared" si="10"/>
         <v>23.890717577353549</v>
       </c>
       <c r="X43" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>23.890717577353549</v>
       </c>
       <c r="Y43" s="9">
@@ -11591,7 +11697,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL43" s="9"/>
+      <c r="AL43" s="9">
+        <f t="shared" si="13"/>
+        <v>0.60759999999999936</v>
+      </c>
       <c r="AM43" s="9"/>
       <c r="AN43" s="9"/>
       <c r="AO43" s="9"/>
@@ -11639,11 +11748,11 @@
         <v>1259</v>
       </c>
       <c r="L44" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-168</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1035</v>
       </c>
       <c r="N44" s="9">
@@ -11656,11 +11765,11 @@
         <v>398</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>207</v>
       </c>
       <c r="R44" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1453</v>
       </c>
       <c r="S44" s="4">
@@ -11672,16 +11781,16 @@
         <v>726</v>
       </c>
       <c r="U44" s="4">
-        <f t="shared" ref="U44:U45" si="23">ROUND(S44*$U$1,0)</f>
+        <f t="shared" ref="U44:U45" si="24">ROUND(S44*$U$1,0)</f>
         <v>727</v>
       </c>
-      <c r="V44" s="22"/>
+      <c r="V44" s="9"/>
       <c r="W44" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X44" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.9806763285024154</v>
       </c>
       <c r="Y44" s="9">
@@ -11723,7 +11832,10 @@
         <f t="shared" si="12"/>
         <v>254.45</v>
       </c>
-      <c r="AL44" s="9"/>
+      <c r="AL44" s="9">
+        <f t="shared" si="13"/>
+        <v>72.449999999999989</v>
+      </c>
       <c r="AM44" s="9"/>
       <c r="AN44" s="9"/>
       <c r="AO44" s="9"/>
@@ -11771,11 +11883,11 @@
         <v>279</v>
       </c>
       <c r="L45" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-52</v>
       </c>
       <c r="M45" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>227</v>
       </c>
       <c r="N45" s="9"/>
@@ -11784,11 +11896,11 @@
       </c>
       <c r="P45" s="9"/>
       <c r="Q45" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>45.4</v>
       </c>
       <c r="R45" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>323</v>
       </c>
       <c r="S45" s="4">
@@ -11800,16 +11912,16 @@
         <v>161</v>
       </c>
       <c r="U45" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>162</v>
       </c>
-      <c r="V45" s="22"/>
+      <c r="V45" s="9"/>
       <c r="W45" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X45" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.8854625550660797</v>
       </c>
       <c r="Y45" s="9">
@@ -11851,7 +11963,10 @@
         <f t="shared" si="12"/>
         <v>66.42</v>
       </c>
-      <c r="AL45" s="9"/>
+      <c r="AL45" s="9">
+        <f t="shared" si="13"/>
+        <v>18.613999999999997</v>
+      </c>
       <c r="AM45" s="9"/>
       <c r="AN45" s="9"/>
       <c r="AO45" s="9"/>
@@ -11899,11 +12014,11 @@
         <v>157</v>
       </c>
       <c r="L46" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-66</v>
       </c>
       <c r="M46" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>91</v>
       </c>
       <c r="N46" s="9"/>
@@ -11912,11 +12027,11 @@
       </c>
       <c r="P46" s="9"/>
       <c r="Q46" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>18.2</v>
       </c>
       <c r="R46" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>77</v>
       </c>
       <c r="S46" s="4">
@@ -11928,13 +12043,13 @@
         <v>77</v>
       </c>
       <c r="U46" s="4"/>
-      <c r="V46" s="22"/>
+      <c r="V46" s="9"/>
       <c r="W46" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.76923076923077</v>
       </c>
       <c r="Y46" s="9">
@@ -11976,7 +12091,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL46" s="9"/>
+      <c r="AL46" s="9">
+        <f t="shared" si="13"/>
+        <v>7.4619999999999989</v>
+      </c>
       <c r="AM46" s="9"/>
       <c r="AN46" s="9"/>
       <c r="AO46" s="9"/>
@@ -12018,11 +12136,11 @@
         <v>8</v>
       </c>
       <c r="L47" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M47" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N47" s="15">
@@ -12033,7 +12151,7 @@
       </c>
       <c r="P47" s="15"/>
       <c r="Q47" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R47" s="18"/>
@@ -12046,13 +12164,13 @@
         <v>0</v>
       </c>
       <c r="U47" s="4"/>
-      <c r="V47" s="22"/>
+      <c r="V47" s="9"/>
       <c r="W47" s="9" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X47" s="15" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y47" s="15">
@@ -12094,7 +12212,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL47" s="9"/>
+      <c r="AL47" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM47" s="9"/>
       <c r="AN47" s="9"/>
       <c r="AO47" s="9"/>
@@ -12142,11 +12263,11 @@
         <v>256</v>
       </c>
       <c r="L48" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-74</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>182</v>
       </c>
       <c r="N48" s="9"/>
@@ -12155,11 +12276,11 @@
       </c>
       <c r="P48" s="9"/>
       <c r="Q48" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.4</v>
       </c>
       <c r="R48" s="4">
-        <f t="shared" ref="R48:R54" si="24">15*Q48-P48-O48-F48</f>
+        <f t="shared" ref="R48:R54" si="25">15*Q48-P48-O48-F48</f>
         <v>29</v>
       </c>
       <c r="S48" s="4">
@@ -12171,13 +12292,13 @@
         <v>29</v>
       </c>
       <c r="U48" s="4"/>
-      <c r="V48" s="22"/>
+      <c r="V48" s="9"/>
       <c r="W48" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X48" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14.203296703296704</v>
       </c>
       <c r="Y48" s="9">
@@ -12219,7 +12340,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL48" s="9"/>
+      <c r="AL48" s="9">
+        <f t="shared" si="13"/>
+        <v>13.103999999999999</v>
+      </c>
       <c r="AM48" s="9"/>
       <c r="AN48" s="9"/>
       <c r="AO48" s="9"/>
@@ -12267,11 +12391,11 @@
         <v>299</v>
       </c>
       <c r="L49" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-83</v>
       </c>
       <c r="M49" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>216</v>
       </c>
       <c r="N49" s="9"/>
@@ -12282,11 +12406,11 @@
         <v>194</v>
       </c>
       <c r="Q49" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43.2</v>
       </c>
       <c r="R49" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>209</v>
       </c>
       <c r="S49" s="4">
@@ -12301,13 +12425,13 @@
         <f>ROUND(S49*$U$1,0)</f>
         <v>105</v>
       </c>
-      <c r="V49" s="22"/>
+      <c r="V49" s="9"/>
       <c r="W49" s="9">
         <f t="shared" si="10"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X49" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.162037037037036</v>
       </c>
       <c r="Y49" s="9">
@@ -12349,7 +12473,10 @@
         <f t="shared" si="12"/>
         <v>34.65</v>
       </c>
-      <c r="AL49" s="9"/>
+      <c r="AL49" s="9">
+        <f t="shared" si="13"/>
+        <v>14.256000000000002</v>
+      </c>
       <c r="AM49" s="9"/>
       <c r="AN49" s="9"/>
       <c r="AO49" s="9"/>
@@ -12397,11 +12524,11 @@
         <v>237</v>
       </c>
       <c r="L50" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-152</v>
       </c>
       <c r="M50" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>53</v>
       </c>
       <c r="N50" s="9">
@@ -12412,7 +12539,7 @@
       </c>
       <c r="P50" s="9"/>
       <c r="Q50" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.6</v>
       </c>
       <c r="R50" s="4"/>
@@ -12425,13 +12552,13 @@
         <v>0</v>
       </c>
       <c r="U50" s="4"/>
-      <c r="V50" s="22"/>
+      <c r="V50" s="9"/>
       <c r="W50" s="9">
         <f t="shared" si="10"/>
         <v>19.245283018867926</v>
       </c>
       <c r="X50" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19.245283018867926</v>
       </c>
       <c r="Y50" s="9">
@@ -12475,7 +12602,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL50" s="9"/>
+      <c r="AL50" s="9">
+        <f t="shared" si="13"/>
+        <v>4.24</v>
+      </c>
       <c r="AM50" s="9"/>
       <c r="AN50" s="9"/>
       <c r="AO50" s="9"/>
@@ -12519,11 +12649,11 @@
         <v>21</v>
       </c>
       <c r="L51" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-16</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="N51" s="9"/>
@@ -12532,7 +12662,7 @@
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="R51" s="4"/>
@@ -12545,13 +12675,13 @@
         <v>0</v>
       </c>
       <c r="U51" s="4"/>
-      <c r="V51" s="22"/>
+      <c r="V51" s="9"/>
       <c r="W51" s="9">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
       <c r="X51" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46</v>
       </c>
       <c r="Y51" s="9">
@@ -12593,7 +12723,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL51" s="9"/>
+      <c r="AL51" s="9">
+        <f t="shared" si="13"/>
+        <v>0.33</v>
+      </c>
       <c r="AM51" s="9"/>
       <c r="AN51" s="9"/>
       <c r="AO51" s="9"/>
@@ -12641,11 +12774,11 @@
         <v>562.13800000000003</v>
       </c>
       <c r="L52" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-23.966000000000008</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>436.63400000000001</v>
       </c>
       <c r="N52" s="9">
@@ -12658,11 +12791,11 @@
         <v>348</v>
       </c>
       <c r="Q52" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>87.326800000000006</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>165.64600000000007</v>
       </c>
       <c r="S52" s="4">
@@ -12674,13 +12807,13 @@
         <v>166</v>
       </c>
       <c r="U52" s="4"/>
-      <c r="V52" s="22"/>
+      <c r="V52" s="9"/>
       <c r="W52" s="9">
         <f t="shared" si="10"/>
         <v>15.004053738371265</v>
       </c>
       <c r="X52" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.103148174443582</v>
       </c>
       <c r="Y52" s="9">
@@ -12722,7 +12855,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL52" s="9"/>
+      <c r="AL52" s="9">
+        <f t="shared" si="13"/>
+        <v>87.326800000000006</v>
+      </c>
       <c r="AM52" s="9"/>
       <c r="AN52" s="9"/>
       <c r="AO52" s="9"/>
@@ -12770,11 +12906,11 @@
         <v>43</v>
       </c>
       <c r="L53" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-16</v>
       </c>
       <c r="M53" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>27</v>
       </c>
       <c r="N53" s="9"/>
@@ -12783,11 +12919,11 @@
       </c>
       <c r="P53" s="9"/>
       <c r="Q53" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.4</v>
       </c>
       <c r="R53" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
       <c r="S53" s="4">
@@ -12799,13 +12935,13 @@
         <v>29</v>
       </c>
       <c r="U53" s="4"/>
-      <c r="V53" s="22"/>
+      <c r="V53" s="9"/>
       <c r="W53" s="9">
         <f t="shared" si="10"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X53" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.6296296296296298</v>
       </c>
       <c r="Y53" s="9">
@@ -12847,7 +12983,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL53" s="9"/>
+      <c r="AL53" s="9">
+        <f t="shared" si="13"/>
+        <v>2.16</v>
+      </c>
       <c r="AM53" s="9"/>
       <c r="AN53" s="9"/>
       <c r="AO53" s="9"/>
@@ -12891,11 +13030,11 @@
         <v>23.7</v>
       </c>
       <c r="L54" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-4.9659999999999975</v>
       </c>
       <c r="M54" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>18.734000000000002</v>
       </c>
       <c r="N54" s="9"/>
@@ -12904,11 +13043,11 @@
       </c>
       <c r="P54" s="9"/>
       <c r="Q54" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.7468000000000004</v>
       </c>
       <c r="R54" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>15.202000000000005</v>
       </c>
       <c r="S54" s="4">
@@ -12920,13 +13059,13 @@
         <v>15</v>
       </c>
       <c r="U54" s="4"/>
-      <c r="V54" s="22"/>
+      <c r="V54" s="9"/>
       <c r="W54" s="9">
         <f t="shared" si="10"/>
         <v>14.9460873278531</v>
       </c>
       <c r="X54" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.94267107932102</v>
       </c>
       <c r="Y54" s="9">
@@ -12968,7 +13107,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL54" s="9"/>
+      <c r="AL54" s="9">
+        <f t="shared" si="13"/>
+        <v>3.7468000000000004</v>
+      </c>
       <c r="AM54" s="9"/>
       <c r="AN54" s="9"/>
       <c r="AO54" s="9"/>
@@ -13016,11 +13158,11 @@
         <v>27</v>
       </c>
       <c r="L55" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.4789999999999992</v>
       </c>
       <c r="M55" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>27.478999999999999</v>
       </c>
       <c r="N55" s="9"/>
@@ -13029,7 +13171,7 @@
       </c>
       <c r="P55" s="9"/>
       <c r="Q55" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.4958</v>
       </c>
       <c r="R55" s="4">
@@ -13045,13 +13187,13 @@
         <v>49</v>
       </c>
       <c r="U55" s="4"/>
-      <c r="V55" s="22"/>
+      <c r="V55" s="9"/>
       <c r="W55" s="9">
         <f t="shared" si="10"/>
         <v>12.926052622002256</v>
       </c>
       <c r="X55" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.0101532079042181</v>
       </c>
       <c r="Y55" s="9">
@@ -13093,7 +13235,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL55" s="9"/>
+      <c r="AL55" s="9">
+        <f t="shared" si="13"/>
+        <v>5.4958</v>
+      </c>
       <c r="AM55" s="9"/>
       <c r="AN55" s="9"/>
       <c r="AO55" s="9"/>
@@ -13137,11 +13282,11 @@
         <v>7</v>
       </c>
       <c r="L56" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-7</v>
       </c>
       <c r="M56" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N56" s="15"/>
@@ -13150,7 +13295,7 @@
       </c>
       <c r="P56" s="15"/>
       <c r="Q56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R56" s="18"/>
@@ -13163,13 +13308,13 @@
         <v>0</v>
       </c>
       <c r="U56" s="4"/>
-      <c r="V56" s="22"/>
+      <c r="V56" s="9"/>
       <c r="W56" s="9" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X56" s="15" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y56" s="15">
@@ -13211,7 +13356,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL56" s="9"/>
+      <c r="AL56" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM56" s="9"/>
       <c r="AN56" s="9"/>
       <c r="AO56" s="9"/>
@@ -13259,11 +13407,11 @@
         <v>6.5</v>
       </c>
       <c r="L57" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3.9319999999999999</v>
       </c>
       <c r="M57" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.5680000000000001</v>
       </c>
       <c r="N57" s="9"/>
@@ -13272,7 +13420,7 @@
       </c>
       <c r="P57" s="9"/>
       <c r="Q57" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.51360000000000006</v>
       </c>
       <c r="R57" s="4"/>
@@ -13285,13 +13433,13 @@
         <v>0</v>
       </c>
       <c r="U57" s="4"/>
-      <c r="V57" s="22"/>
+      <c r="V57" s="9"/>
       <c r="W57" s="9">
         <f t="shared" si="10"/>
         <v>165.49649532710276</v>
       </c>
       <c r="X57" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>165.49649532710276</v>
       </c>
       <c r="Y57" s="9">
@@ -13335,7 +13483,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL57" s="9"/>
+      <c r="AL57" s="9">
+        <f t="shared" si="13"/>
+        <v>0.51360000000000006</v>
+      </c>
       <c r="AM57" s="9"/>
       <c r="AN57" s="9"/>
       <c r="AO57" s="9"/>
@@ -13377,11 +13528,11 @@
         <v>56</v>
       </c>
       <c r="L58" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M58" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N58" s="15">
@@ -13390,7 +13541,7 @@
       <c r="O58" s="15"/>
       <c r="P58" s="15"/>
       <c r="Q58" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R58" s="18"/>
@@ -13403,13 +13554,13 @@
         <v>0</v>
       </c>
       <c r="U58" s="4"/>
-      <c r="V58" s="22"/>
+      <c r="V58" s="9"/>
       <c r="W58" s="9" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X58" s="15" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y58" s="15">
@@ -13451,7 +13602,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL58" s="9"/>
+      <c r="AL58" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM58" s="9"/>
       <c r="AN58" s="9"/>
       <c r="AO58" s="9"/>
@@ -13499,11 +13653,11 @@
         <v>53</v>
       </c>
       <c r="L59" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-8</v>
       </c>
       <c r="M59" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>29</v>
       </c>
       <c r="N59" s="9">
@@ -13514,7 +13668,7 @@
       </c>
       <c r="P59" s="9"/>
       <c r="Q59" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.8</v>
       </c>
       <c r="R59" s="4"/>
@@ -13527,13 +13681,13 @@
         <v>0</v>
       </c>
       <c r="U59" s="4"/>
-      <c r="V59" s="22"/>
+      <c r="V59" s="9"/>
       <c r="W59" s="9">
         <f t="shared" si="10"/>
         <v>22.586206896551726</v>
       </c>
       <c r="X59" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>22.586206896551726</v>
       </c>
       <c r="Y59" s="9">
@@ -13577,7 +13731,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL59" s="9"/>
+      <c r="AL59" s="9">
+        <f t="shared" si="13"/>
+        <v>1.45</v>
+      </c>
       <c r="AM59" s="9"/>
       <c r="AN59" s="9"/>
       <c r="AO59" s="9"/>
@@ -13625,11 +13782,11 @@
         <v>16.363</v>
       </c>
       <c r="L60" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.67900000000000027</v>
       </c>
       <c r="M60" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.683999999999999</v>
       </c>
       <c r="N60" s="9"/>
@@ -13638,11 +13795,11 @@
       </c>
       <c r="P60" s="9"/>
       <c r="Q60" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.1368</v>
       </c>
       <c r="R60" s="4">
-        <f t="shared" ref="R60:R63" si="25">15*Q60-P60-O60-F60</f>
+        <f t="shared" ref="R60:R63" si="26">15*Q60-P60-O60-F60</f>
         <v>11.514999999999999</v>
       </c>
       <c r="S60" s="4">
@@ -13654,13 +13811,13 @@
         <v>12</v>
       </c>
       <c r="U60" s="4"/>
-      <c r="V60" s="22"/>
+      <c r="V60" s="9"/>
       <c r="W60" s="9">
         <f t="shared" si="10"/>
         <v>15.154616169344555</v>
       </c>
       <c r="X60" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11.329061463912266</v>
       </c>
       <c r="Y60" s="9">
@@ -13702,7 +13859,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL60" s="9"/>
+      <c r="AL60" s="9">
+        <f t="shared" si="13"/>
+        <v>3.1368</v>
+      </c>
       <c r="AM60" s="9"/>
       <c r="AN60" s="9"/>
       <c r="AO60" s="9"/>
@@ -13748,11 +13908,11 @@
         <v>25</v>
       </c>
       <c r="L61" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-9</v>
       </c>
       <c r="M61" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16</v>
       </c>
       <c r="N61" s="9"/>
@@ -13761,7 +13921,7 @@
       </c>
       <c r="P61" s="9"/>
       <c r="Q61" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.2</v>
       </c>
       <c r="R61" s="4"/>
@@ -13774,13 +13934,13 @@
         <v>0</v>
       </c>
       <c r="U61" s="4"/>
-      <c r="V61" s="22"/>
+      <c r="V61" s="9"/>
       <c r="W61" s="9">
         <f t="shared" si="10"/>
         <v>27.1875</v>
       </c>
       <c r="X61" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>27.1875</v>
       </c>
       <c r="Y61" s="9">
@@ -13824,7 +13984,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL61" s="9"/>
+      <c r="AL61" s="9">
+        <f t="shared" si="13"/>
+        <v>0.8640000000000001</v>
+      </c>
       <c r="AM61" s="9"/>
       <c r="AN61" s="9"/>
       <c r="AO61" s="9"/>
@@ -13872,11 +14035,11 @@
         <v>88</v>
       </c>
       <c r="L62" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-2</v>
       </c>
       <c r="M62" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>86</v>
       </c>
       <c r="N62" s="9"/>
@@ -13885,11 +14048,11 @@
       </c>
       <c r="P62" s="9"/>
       <c r="Q62" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17.2</v>
       </c>
       <c r="R62" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>95</v>
       </c>
       <c r="S62" s="4">
@@ -13901,13 +14064,13 @@
         <v>95</v>
       </c>
       <c r="U62" s="4"/>
-      <c r="V62" s="22"/>
+      <c r="V62" s="9"/>
       <c r="W62" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X62" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.4767441860465116</v>
       </c>
       <c r="Y62" s="9">
@@ -13949,7 +14112,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL62" s="9"/>
+      <c r="AL62" s="9">
+        <f t="shared" si="13"/>
+        <v>5.1599999999999993</v>
+      </c>
       <c r="AM62" s="9"/>
       <c r="AN62" s="9"/>
       <c r="AO62" s="9"/>
@@ -13997,11 +14163,11 @@
         <v>1554</v>
       </c>
       <c r="L63" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-186</v>
       </c>
       <c r="M63" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1368</v>
       </c>
       <c r="N63" s="9"/>
@@ -14012,11 +14178,11 @@
         <v>416</v>
       </c>
       <c r="Q63" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>273.60000000000002</v>
       </c>
       <c r="R63" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1435</v>
       </c>
       <c r="S63" s="4">
@@ -14031,13 +14197,13 @@
         <f>ROUND(S63*$U$1,0)</f>
         <v>718</v>
       </c>
-      <c r="V63" s="22"/>
+      <c r="V63" s="9"/>
       <c r="W63" s="9">
         <f t="shared" si="10"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X63" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.7551169590643259</v>
       </c>
       <c r="Y63" s="9">
@@ -14079,7 +14245,10 @@
         <f t="shared" si="12"/>
         <v>294.38</v>
       </c>
-      <c r="AL63" s="9"/>
+      <c r="AL63" s="9">
+        <f t="shared" si="13"/>
+        <v>112.176</v>
+      </c>
       <c r="AM63" s="9"/>
       <c r="AN63" s="9"/>
       <c r="AO63" s="9"/>
@@ -14127,11 +14296,11 @@
         <v>423.577</v>
       </c>
       <c r="L64" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.146000000000015</v>
       </c>
       <c r="M64" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>324.94600000000003</v>
       </c>
       <c r="N64" s="9">
@@ -14142,7 +14311,7 @@
       </c>
       <c r="P64" s="9"/>
       <c r="Q64" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>64.989200000000011</v>
       </c>
       <c r="R64" s="4"/>
@@ -14155,7 +14324,7 @@
         <v>120</v>
       </c>
       <c r="U64" s="4"/>
-      <c r="V64" s="22">
+      <c r="V64" s="9">
         <f>VLOOKUP(A64,[1]Sheet!$A:$S,19,0)</f>
         <v>120</v>
       </c>
@@ -14164,7 +14333,7 @@
         <v>17.437512694416917</v>
       </c>
       <c r="X64" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>15.591052051725514</v>
       </c>
       <c r="Y64" s="9">
@@ -14206,7 +14375,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL64" s="9"/>
+      <c r="AL64" s="9">
+        <f t="shared" si="13"/>
+        <v>64.989200000000011</v>
+      </c>
       <c r="AM64" s="9"/>
       <c r="AN64" s="9"/>
       <c r="AO64" s="9"/>
@@ -14252,11 +14424,11 @@
         <v>41</v>
       </c>
       <c r="L65" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M65" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>41</v>
       </c>
       <c r="N65" s="9"/>
@@ -14265,7 +14437,7 @@
       </c>
       <c r="P65" s="9"/>
       <c r="Q65" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="R65" s="4">
@@ -14280,13 +14452,13 @@
         <v>16</v>
       </c>
       <c r="U65" s="4"/>
-      <c r="V65" s="22"/>
+      <c r="V65" s="9"/>
       <c r="W65" s="9">
         <f t="shared" si="10"/>
         <v>16.707317073170731</v>
       </c>
       <c r="X65" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14.756097560975611</v>
       </c>
       <c r="Y65" s="9">
@@ -14328,7 +14500,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL65" s="9"/>
+      <c r="AL65" s="9">
+        <f t="shared" si="13"/>
+        <v>2.8699999999999997</v>
+      </c>
       <c r="AM65" s="9"/>
       <c r="AN65" s="9"/>
       <c r="AO65" s="9"/>
@@ -14364,11 +14539,11 @@
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
       <c r="L66" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M66" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N66" s="15"/>
@@ -14377,7 +14552,7 @@
       </c>
       <c r="P66" s="15"/>
       <c r="Q66" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R66" s="18"/>
@@ -14390,13 +14565,13 @@
         <v>0</v>
       </c>
       <c r="U66" s="4"/>
-      <c r="V66" s="22"/>
+      <c r="V66" s="9"/>
       <c r="W66" s="9" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X66" s="15" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y66" s="15">
@@ -14440,7 +14615,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL66" s="9"/>
+      <c r="AL66" s="9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM66" s="9"/>
       <c r="AN66" s="9"/>
       <c r="AO66" s="9"/>
@@ -14488,11 +14666,11 @@
         <v>1205</v>
       </c>
       <c r="L67" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-428</v>
       </c>
       <c r="M67" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>777</v>
       </c>
       <c r="N67" s="9"/>
@@ -14503,7 +14681,7 @@
         <v>138</v>
       </c>
       <c r="Q67" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>155.4</v>
       </c>
       <c r="R67" s="4">
@@ -14511,7 +14689,7 @@
         <v>1423.4</v>
       </c>
       <c r="S67" s="4">
-        <f t="shared" ref="S67:S68" si="26">V67</f>
+        <f t="shared" ref="S67:S68" si="27">V67</f>
         <v>1500</v>
       </c>
       <c r="T67" s="4">
@@ -14522,7 +14700,7 @@
         <f>ROUND(S67*$U$1,0)</f>
         <v>750</v>
       </c>
-      <c r="V67" s="22">
+      <c r="V67" s="9">
         <f>VLOOKUP(A67,[1]Sheet!$A:$S,19,0)</f>
         <v>1500</v>
       </c>
@@ -14531,7 +14709,7 @@
         <v>11.492921492921493</v>
       </c>
       <c r="X67" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.8404118404118404</v>
       </c>
       <c r="Y67" s="9">
@@ -14573,7 +14751,10 @@
         <f t="shared" si="12"/>
         <v>307.5</v>
       </c>
-      <c r="AL67" s="9"/>
+      <c r="AL67" s="9">
+        <f t="shared" si="13"/>
+        <v>63.713999999999999</v>
+      </c>
       <c r="AM67" s="9"/>
       <c r="AN67" s="9"/>
       <c r="AO67" s="9"/>
@@ -14621,11 +14802,11 @@
         <v>134.285</v>
       </c>
       <c r="L68" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4.6069999999999993</v>
       </c>
       <c r="M68" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>114.407</v>
       </c>
       <c r="N68" s="9">
@@ -14636,7 +14817,7 @@
       </c>
       <c r="P68" s="9"/>
       <c r="Q68" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.881399999999999</v>
       </c>
       <c r="R68" s="4">
@@ -14644,7 +14825,7 @@
         <v>42.897000000000006</v>
       </c>
       <c r="S68" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
       <c r="T68" s="4">
@@ -14652,7 +14833,7 @@
         <v>70</v>
       </c>
       <c r="U68" s="4"/>
-      <c r="V68" s="22">
+      <c r="V68" s="9">
         <f>VLOOKUP(A68,[1]Sheet!$A:$S,19,0)</f>
         <v>70</v>
       </c>
@@ -14661,7 +14842,7 @@
         <v>16.184499200223765</v>
       </c>
       <c r="X68" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.125245832859878</v>
       </c>
       <c r="Y68" s="9">
@@ -14703,7 +14884,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL68" s="9"/>
+      <c r="AL68" s="9">
+        <f t="shared" si="13"/>
+        <v>22.881399999999999</v>
+      </c>
       <c r="AM68" s="9"/>
       <c r="AN68" s="9"/>
       <c r="AO68" s="9"/>
@@ -14751,11 +14935,11 @@
         <v>225</v>
       </c>
       <c r="L69" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-55</v>
       </c>
       <c r="M69" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>122</v>
       </c>
       <c r="N69" s="9">
@@ -14766,7 +14950,7 @@
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24.4</v>
       </c>
       <c r="R69" s="4">
@@ -14782,13 +14966,13 @@
         <v>130</v>
       </c>
       <c r="U69" s="4"/>
-      <c r="V69" s="22"/>
+      <c r="V69" s="9"/>
       <c r="W69" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X69" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.6721311475409841</v>
       </c>
       <c r="Y69" s="9">
@@ -14830,7 +15014,10 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL69" s="9"/>
+      <c r="AL69" s="9">
+        <f t="shared" si="13"/>
+        <v>7.3199999999999994</v>
+      </c>
       <c r="AM69" s="9"/>
       <c r="AN69" s="9"/>
       <c r="AO69" s="9"/>
@@ -14880,11 +15067,11 @@
         <v>312</v>
       </c>
       <c r="L70" s="9">
-        <f t="shared" ref="L70:L101" si="27">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="28">E70-K70</f>
         <v>-90</v>
       </c>
       <c r="M70" s="9">
-        <f t="shared" ref="M70:M101" si="28">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="29">E70-N70</f>
         <v>182</v>
       </c>
       <c r="N70" s="9">
@@ -14895,7 +15082,7 @@
       </c>
       <c r="P70" s="9"/>
       <c r="Q70" s="9">
-        <f t="shared" ref="Q70:Q101" si="29">M70/5</f>
+        <f t="shared" ref="Q70:Q101" si="30">M70/5</f>
         <v>36.4</v>
       </c>
       <c r="R70" s="4">
@@ -14914,13 +15101,13 @@
         <f>ROUND(S70*$U$1,0)</f>
         <v>144</v>
       </c>
-      <c r="V70" s="22"/>
+      <c r="V70" s="9"/>
       <c r="W70" s="9">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="X70" s="9">
-        <f t="shared" ref="X70:X101" si="30">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="X70:X101" si="31">(F70+O70+P70)/Q70</f>
         <v>7.0879120879120885</v>
       </c>
       <c r="Y70" s="9">
@@ -14962,7 +15149,10 @@
         <f t="shared" si="12"/>
         <v>25.919999999999998</v>
       </c>
-      <c r="AL70" s="9"/>
+      <c r="AL70" s="9">
+        <f t="shared" si="13"/>
+        <v>6.5519999999999996</v>
+      </c>
       <c r="AM70" s="9"/>
       <c r="AN70" s="9"/>
       <c r="AO70" s="9"/>
@@ -15008,11 +15198,11 @@
         <v>8</v>
       </c>
       <c r="L71" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-3</v>
       </c>
       <c r="M71" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="N71" s="9"/>
@@ -15021,26 +15211,26 @@
       </c>
       <c r="P71" s="9"/>
       <c r="Q71" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="R71" s="4"/>
       <c r="S71" s="4">
-        <f t="shared" ref="S71:S117" si="31">ROUND(R71,0)</f>
+        <f t="shared" ref="S71:S117" si="32">ROUND(R71,0)</f>
         <v>0</v>
       </c>
       <c r="T71" s="4">
-        <f t="shared" ref="T71:T117" si="32">ROUND(S71-U71,0)</f>
+        <f t="shared" ref="T71:T117" si="33">ROUND(S71-U71,0)</f>
         <v>0</v>
       </c>
       <c r="U71" s="4"/>
-      <c r="V71" s="22"/>
+      <c r="V71" s="9"/>
       <c r="W71" s="9">
-        <f t="shared" ref="W71:W117" si="33">(F71+O71+P71+S71)/Q71</f>
+        <f t="shared" ref="W71:W117" si="34">(F71+O71+P71+S71)/Q71</f>
         <v>35</v>
       </c>
       <c r="X71" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>35</v>
       </c>
       <c r="Y71" s="9">
@@ -15077,14 +15267,17 @@
         <v>37</v>
       </c>
       <c r="AJ71" s="9">
-        <f t="shared" ref="AJ71:AJ117" si="34">G71*T71</f>
+        <f t="shared" ref="AJ71:AJ117" si="35">G71*T71</f>
         <v>0</v>
       </c>
       <c r="AK71" s="9">
-        <f t="shared" ref="AK71:AK117" si="35">G71*U71</f>
-        <v>0</v>
-      </c>
-      <c r="AL71" s="9"/>
+        <f t="shared" ref="AK71:AK117" si="36">G71*U71</f>
+        <v>0</v>
+      </c>
+      <c r="AL71" s="9">
+        <f t="shared" ref="AL71:AL117" si="37">Q71*G71</f>
+        <v>0.22</v>
+      </c>
       <c r="AM71" s="9"/>
       <c r="AN71" s="9"/>
       <c r="AO71" s="9"/>
@@ -15126,13 +15319,13 @@
         <v>32</v>
       </c>
       <c r="L72" s="15">
-        <f t="shared" si="27"/>
-        <v>-3</v>
-      </c>
-      <c r="M72" s="15">
         <f t="shared" si="28"/>
         <v>-3</v>
       </c>
+      <c r="M72" s="15">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
       <c r="N72" s="15">
         <v>32</v>
       </c>
@@ -15141,26 +15334,26 @@
       </c>
       <c r="P72" s="15"/>
       <c r="Q72" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-0.6</v>
       </c>
       <c r="R72" s="18"/>
       <c r="S72" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T72" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U72" s="4"/>
+      <c r="V72" s="9"/>
+      <c r="W72" s="9">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X72" s="15">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T72" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U72" s="4"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="9">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X72" s="15">
-        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y72" s="15">
@@ -15195,14 +15388,17 @@
       </c>
       <c r="AI72" s="15"/>
       <c r="AJ72" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK72" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL72" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL72" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM72" s="9"/>
       <c r="AN72" s="9"/>
       <c r="AO72" s="9"/>
@@ -15244,11 +15440,11 @@
         <v>32</v>
       </c>
       <c r="L73" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-2</v>
       </c>
       <c r="M73" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N73" s="15">
@@ -15259,26 +15455,26 @@
       </c>
       <c r="P73" s="15"/>
       <c r="Q73" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R73" s="18"/>
       <c r="S73" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T73" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="4"/>
+      <c r="V73" s="9"/>
+      <c r="W73" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X73" s="15" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T73" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U73" s="4"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X73" s="15" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y73" s="15">
@@ -15315,14 +15511,17 @@
         <v>112</v>
       </c>
       <c r="AJ73" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK73" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL73" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL73" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
       <c r="AO73" s="9"/>
@@ -15370,11 +15569,11 @@
         <v>993</v>
       </c>
       <c r="L74" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-99</v>
       </c>
       <c r="M74" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>814</v>
       </c>
       <c r="N74" s="9">
@@ -15387,7 +15586,7 @@
         <v>218</v>
       </c>
       <c r="Q74" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>162.80000000000001</v>
       </c>
       <c r="R74" s="4">
@@ -15395,24 +15594,24 @@
         <v>840</v>
       </c>
       <c r="S74" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>840</v>
       </c>
       <c r="T74" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>420</v>
       </c>
       <c r="U74" s="4">
         <f>ROUND(S74*$U$1,0)</f>
         <v>420</v>
       </c>
-      <c r="V74" s="22"/>
+      <c r="V74" s="9"/>
       <c r="W74" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X74" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.84029484029484</v>
       </c>
       <c r="Y74" s="9">
@@ -15447,14 +15646,17 @@
       </c>
       <c r="AI74" s="9"/>
       <c r="AJ74" s="9">
-        <f t="shared" si="34"/>
-        <v>147</v>
-      </c>
-      <c r="AK74" s="9">
         <f t="shared" si="35"/>
         <v>147</v>
       </c>
-      <c r="AL74" s="9"/>
+      <c r="AK74" s="9">
+        <f t="shared" si="36"/>
+        <v>147</v>
+      </c>
+      <c r="AL74" s="9">
+        <f t="shared" si="37"/>
+        <v>56.98</v>
+      </c>
       <c r="AM74" s="9"/>
       <c r="AN74" s="9"/>
       <c r="AO74" s="9"/>
@@ -15498,11 +15700,11 @@
         <v>34</v>
       </c>
       <c r="L75" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-3</v>
       </c>
       <c r="M75" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>31</v>
       </c>
       <c r="N75" s="9"/>
@@ -15511,26 +15713,26 @@
       </c>
       <c r="P75" s="9"/>
       <c r="Q75" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.2</v>
       </c>
       <c r="R75" s="4"/>
       <c r="S75" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T75" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U75" s="4"/>
+      <c r="V75" s="9"/>
+      <c r="W75" s="9">
+        <f t="shared" si="34"/>
+        <v>25.322580645161288</v>
+      </c>
+      <c r="X75" s="9">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T75" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U75" s="4"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="9">
-        <f t="shared" si="33"/>
-        <v>25.322580645161288</v>
-      </c>
-      <c r="X75" s="9">
-        <f t="shared" si="30"/>
         <v>25.322580645161288</v>
       </c>
       <c r="Y75" s="9">
@@ -15567,14 +15769,17 @@
         <v>86</v>
       </c>
       <c r="AJ75" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK75" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL75" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL75" s="9">
+        <f t="shared" si="37"/>
+        <v>2.17</v>
+      </c>
       <c r="AM75" s="9"/>
       <c r="AN75" s="9"/>
       <c r="AO75" s="9"/>
@@ -15622,11 +15827,11 @@
         <v>215.72200000000001</v>
       </c>
       <c r="L76" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>10.138000000000005</v>
       </c>
       <c r="M76" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>182.53800000000001</v>
       </c>
       <c r="N76" s="9">
@@ -15637,7 +15842,7 @@
       </c>
       <c r="P76" s="9"/>
       <c r="Q76" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>36.507600000000004</v>
       </c>
       <c r="R76" s="4">
@@ -15645,21 +15850,21 @@
         <v>169.34700000000004</v>
       </c>
       <c r="S76" s="4">
-        <f t="shared" si="31"/>
-        <v>169</v>
-      </c>
-      <c r="T76" s="4">
         <f t="shared" si="32"/>
         <v>169</v>
       </c>
+      <c r="T76" s="4">
+        <f t="shared" si="33"/>
+        <v>169</v>
+      </c>
       <c r="U76" s="4"/>
-      <c r="V76" s="22"/>
+      <c r="V76" s="9"/>
       <c r="W76" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>14.990495129781197</v>
       </c>
       <c r="X76" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>10.361322026098675</v>
       </c>
       <c r="Y76" s="9">
@@ -15694,14 +15899,17 @@
       </c>
       <c r="AI76" s="9"/>
       <c r="AJ76" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>169</v>
       </c>
       <c r="AK76" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL76" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL76" s="9">
+        <f t="shared" si="37"/>
+        <v>36.507600000000004</v>
+      </c>
       <c r="AM76" s="9"/>
       <c r="AN76" s="9"/>
       <c r="AO76" s="9"/>
@@ -15743,11 +15951,11 @@
       <c r="J77" s="15"/>
       <c r="K77" s="15"/>
       <c r="L77" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M77" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N77" s="15"/>
@@ -15756,26 +15964,26 @@
       </c>
       <c r="P77" s="15"/>
       <c r="Q77" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R77" s="18"/>
       <c r="S77" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T77" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="4"/>
+      <c r="V77" s="9"/>
+      <c r="W77" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X77" s="15" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T77" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U77" s="4"/>
-      <c r="V77" s="22"/>
-      <c r="W77" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X77" s="15" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y77" s="15">
@@ -15812,14 +16020,17 @@
         <v>95</v>
       </c>
       <c r="AJ77" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK77" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL77" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL77" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM77" s="9"/>
       <c r="AN77" s="9"/>
       <c r="AO77" s="9"/>
@@ -15867,11 +16078,11 @@
         <v>386.71600000000001</v>
       </c>
       <c r="L78" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.6419999999999959</v>
       </c>
       <c r="M78" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>345.44200000000001</v>
       </c>
       <c r="N78" s="9">
@@ -15884,32 +16095,32 @@
         <v>222</v>
       </c>
       <c r="Q78" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>69.088400000000007</v>
       </c>
       <c r="R78" s="4">
-        <f t="shared" ref="R78:R85" si="36">15*Q78-P78-O78-F78</f>
+        <f t="shared" ref="R78:R85" si="38">15*Q78-P78-O78-F78</f>
         <v>288.03800000000001</v>
       </c>
       <c r="S78" s="4">
+        <f t="shared" si="32"/>
+        <v>288</v>
+      </c>
+      <c r="T78" s="4">
+        <f t="shared" si="33"/>
+        <v>144</v>
+      </c>
+      <c r="U78" s="4">
+        <f t="shared" ref="U78:U79" si="39">ROUND(S78*$U$1,0)</f>
+        <v>144</v>
+      </c>
+      <c r="V78" s="9"/>
+      <c r="W78" s="9">
+        <f t="shared" si="34"/>
+        <v>14.99944998002559</v>
+      </c>
+      <c r="X78" s="9">
         <f t="shared" si="31"/>
-        <v>288</v>
-      </c>
-      <c r="T78" s="4">
-        <f t="shared" si="32"/>
-        <v>144</v>
-      </c>
-      <c r="U78" s="4">
-        <f t="shared" ref="U78:U79" si="37">ROUND(S78*$U$1,0)</f>
-        <v>144</v>
-      </c>
-      <c r="V78" s="22"/>
-      <c r="W78" s="9">
-        <f t="shared" si="33"/>
-        <v>14.99944998002559</v>
-      </c>
-      <c r="X78" s="9">
-        <f t="shared" si="30"/>
         <v>10.83087754239496</v>
       </c>
       <c r="Y78" s="9">
@@ -15944,14 +16155,17 @@
       </c>
       <c r="AI78" s="9"/>
       <c r="AJ78" s="9">
-        <f t="shared" si="34"/>
-        <v>144</v>
-      </c>
-      <c r="AK78" s="9">
         <f t="shared" si="35"/>
         <v>144</v>
       </c>
-      <c r="AL78" s="9"/>
+      <c r="AK78" s="9">
+        <f t="shared" si="36"/>
+        <v>144</v>
+      </c>
+      <c r="AL78" s="9">
+        <f t="shared" si="37"/>
+        <v>69.088400000000007</v>
+      </c>
       <c r="AM78" s="9"/>
       <c r="AN78" s="9"/>
       <c r="AO78" s="9"/>
@@ -15999,11 +16213,11 @@
         <v>2569</v>
       </c>
       <c r="L79" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-899</v>
       </c>
       <c r="M79" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1630</v>
       </c>
       <c r="N79" s="9">
@@ -16014,7 +16228,7 @@
       </c>
       <c r="P79" s="9"/>
       <c r="Q79" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>326</v>
       </c>
       <c r="R79" s="4">
@@ -16025,23 +16239,23 @@
         <v>1700</v>
       </c>
       <c r="T79" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>850</v>
       </c>
       <c r="U79" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>850</v>
       </c>
-      <c r="V79" s="22">
+      <c r="V79" s="9">
         <f>VLOOKUP(A79,[1]Sheet!$A:$S,19,0)</f>
         <v>1700</v>
       </c>
       <c r="W79" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>8.8527607361963199</v>
       </c>
       <c r="X79" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3.6380368098159508</v>
       </c>
       <c r="Y79" s="9">
@@ -16078,14 +16292,17 @@
         <v>52</v>
       </c>
       <c r="AJ79" s="9">
-        <f t="shared" si="34"/>
-        <v>297.5</v>
-      </c>
-      <c r="AK79" s="9">
         <f t="shared" si="35"/>
         <v>297.5</v>
       </c>
-      <c r="AL79" s="9"/>
+      <c r="AK79" s="9">
+        <f t="shared" si="36"/>
+        <v>297.5</v>
+      </c>
+      <c r="AL79" s="9">
+        <f t="shared" si="37"/>
+        <v>114.1</v>
+      </c>
       <c r="AM79" s="9"/>
       <c r="AN79" s="9"/>
       <c r="AO79" s="9"/>
@@ -16133,11 +16350,11 @@
         <v>167</v>
       </c>
       <c r="L80" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-7</v>
       </c>
       <c r="M80" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>100</v>
       </c>
       <c r="N80" s="9">
@@ -16150,26 +16367,26 @@
         <v>137</v>
       </c>
       <c r="Q80" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="R80" s="4"/>
       <c r="S80" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T80" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U80" s="4"/>
+      <c r="V80" s="9"/>
+      <c r="W80" s="9">
+        <f t="shared" si="34"/>
+        <v>16.2</v>
+      </c>
+      <c r="X80" s="9">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T80" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U80" s="4"/>
-      <c r="V80" s="22"/>
-      <c r="W80" s="9">
-        <f t="shared" si="33"/>
-        <v>16.2</v>
-      </c>
-      <c r="X80" s="9">
-        <f t="shared" si="30"/>
         <v>16.2</v>
       </c>
       <c r="Y80" s="9">
@@ -16204,14 +16421,17 @@
       </c>
       <c r="AI80" s="9"/>
       <c r="AJ80" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK80" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL80" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL80" s="9">
+        <f t="shared" si="37"/>
+        <v>6</v>
+      </c>
       <c r="AM80" s="9"/>
       <c r="AN80" s="9"/>
       <c r="AO80" s="9"/>
@@ -16259,11 +16479,11 @@
         <v>68</v>
       </c>
       <c r="L81" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-32</v>
       </c>
       <c r="M81" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>36</v>
       </c>
       <c r="N81" s="9"/>
@@ -16272,29 +16492,29 @@
       </c>
       <c r="P81" s="9"/>
       <c r="Q81" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.2</v>
       </c>
       <c r="R81" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>17</v>
       </c>
       <c r="S81" s="4">
-        <f t="shared" si="31"/>
-        <v>17</v>
-      </c>
-      <c r="T81" s="4">
         <f t="shared" si="32"/>
         <v>17</v>
       </c>
+      <c r="T81" s="4">
+        <f t="shared" si="33"/>
+        <v>17</v>
+      </c>
       <c r="U81" s="4"/>
-      <c r="V81" s="22"/>
+      <c r="V81" s="9"/>
       <c r="W81" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X81" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>12.638888888888889</v>
       </c>
       <c r="Y81" s="9">
@@ -16329,14 +16549,17 @@
       </c>
       <c r="AI81" s="9"/>
       <c r="AJ81" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="AK81" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL81" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL81" s="9">
+        <f t="shared" si="37"/>
+        <v>2.16</v>
+      </c>
       <c r="AM81" s="9"/>
       <c r="AN81" s="9"/>
       <c r="AO81" s="9"/>
@@ -16384,11 +16607,11 @@
         <v>141</v>
       </c>
       <c r="L82" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-39</v>
       </c>
       <c r="M82" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>102</v>
       </c>
       <c r="N82" s="9"/>
@@ -16397,29 +16620,29 @@
       </c>
       <c r="P82" s="9"/>
       <c r="Q82" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>20.399999999999999</v>
       </c>
       <c r="R82" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>121</v>
       </c>
       <c r="S82" s="4">
-        <f t="shared" si="31"/>
-        <v>121</v>
-      </c>
-      <c r="T82" s="4">
         <f t="shared" si="32"/>
         <v>121</v>
       </c>
+      <c r="T82" s="4">
+        <f t="shared" si="33"/>
+        <v>121</v>
+      </c>
       <c r="U82" s="4"/>
-      <c r="V82" s="22"/>
+      <c r="V82" s="9"/>
       <c r="W82" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15.000000000000002</v>
       </c>
       <c r="X82" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.0686274509803919</v>
       </c>
       <c r="Y82" s="9">
@@ -16454,14 +16677,17 @@
       </c>
       <c r="AI82" s="9"/>
       <c r="AJ82" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>33.880000000000003</v>
       </c>
       <c r="AK82" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL82" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL82" s="9">
+        <f t="shared" si="37"/>
+        <v>5.7119999999999997</v>
+      </c>
       <c r="AM82" s="9"/>
       <c r="AN82" s="9"/>
       <c r="AO82" s="9"/>
@@ -16509,11 +16735,11 @@
         <v>437</v>
       </c>
       <c r="L83" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-133</v>
       </c>
       <c r="M83" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>248</v>
       </c>
       <c r="N83" s="9">
@@ -16524,32 +16750,32 @@
       </c>
       <c r="P83" s="9"/>
       <c r="Q83" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>49.6</v>
       </c>
       <c r="R83" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>226</v>
       </c>
       <c r="S83" s="4">
+        <f t="shared" si="32"/>
+        <v>226</v>
+      </c>
+      <c r="T83" s="4">
+        <f t="shared" si="33"/>
+        <v>113</v>
+      </c>
+      <c r="U83" s="4">
+        <f t="shared" ref="U83:U85" si="40">ROUND(S83*$U$1,0)</f>
+        <v>113</v>
+      </c>
+      <c r="V83" s="9"/>
+      <c r="W83" s="9">
+        <f t="shared" si="34"/>
+        <v>15</v>
+      </c>
+      <c r="X83" s="9">
         <f t="shared" si="31"/>
-        <v>226</v>
-      </c>
-      <c r="T83" s="4">
-        <f t="shared" si="32"/>
-        <v>113</v>
-      </c>
-      <c r="U83" s="4">
-        <f t="shared" ref="U83:U85" si="38">ROUND(S83*$U$1,0)</f>
-        <v>113</v>
-      </c>
-      <c r="V83" s="22"/>
-      <c r="W83" s="9">
-        <f t="shared" si="33"/>
-        <v>15</v>
-      </c>
-      <c r="X83" s="9">
-        <f t="shared" si="30"/>
         <v>10.443548387096774</v>
       </c>
       <c r="Y83" s="9">
@@ -16586,14 +16812,17 @@
         <v>129</v>
       </c>
       <c r="AJ83" s="9">
-        <f t="shared" si="34"/>
-        <v>31.640000000000004</v>
-      </c>
-      <c r="AK83" s="9">
         <f t="shared" si="35"/>
         <v>31.640000000000004</v>
       </c>
-      <c r="AL83" s="9"/>
+      <c r="AK83" s="9">
+        <f t="shared" si="36"/>
+        <v>31.640000000000004</v>
+      </c>
+      <c r="AL83" s="9">
+        <f t="shared" si="37"/>
+        <v>13.888000000000002</v>
+      </c>
       <c r="AM83" s="9"/>
       <c r="AN83" s="9"/>
       <c r="AO83" s="9"/>
@@ -16641,11 +16870,11 @@
         <v>337</v>
       </c>
       <c r="L84" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-87</v>
       </c>
       <c r="M84" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>250</v>
       </c>
       <c r="N84" s="9"/>
@@ -16654,32 +16883,32 @@
       </c>
       <c r="P84" s="9"/>
       <c r="Q84" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>50</v>
       </c>
       <c r="R84" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>236</v>
       </c>
       <c r="S84" s="4">
+        <f t="shared" si="32"/>
+        <v>236</v>
+      </c>
+      <c r="T84" s="4">
+        <f t="shared" si="33"/>
+        <v>118</v>
+      </c>
+      <c r="U84" s="4">
+        <f t="shared" si="40"/>
+        <v>118</v>
+      </c>
+      <c r="V84" s="9"/>
+      <c r="W84" s="9">
+        <f t="shared" si="34"/>
+        <v>15</v>
+      </c>
+      <c r="X84" s="9">
         <f t="shared" si="31"/>
-        <v>236</v>
-      </c>
-      <c r="T84" s="4">
-        <f t="shared" si="32"/>
-        <v>118</v>
-      </c>
-      <c r="U84" s="4">
-        <f t="shared" si="38"/>
-        <v>118</v>
-      </c>
-      <c r="V84" s="22"/>
-      <c r="W84" s="9">
-        <f t="shared" si="33"/>
-        <v>15</v>
-      </c>
-      <c r="X84" s="9">
-        <f t="shared" si="30"/>
         <v>10.28</v>
       </c>
       <c r="Y84" s="9">
@@ -16714,14 +16943,17 @@
       </c>
       <c r="AI84" s="9"/>
       <c r="AJ84" s="9">
-        <f t="shared" si="34"/>
-        <v>33.040000000000006</v>
-      </c>
-      <c r="AK84" s="9">
         <f t="shared" si="35"/>
         <v>33.040000000000006</v>
       </c>
-      <c r="AL84" s="9"/>
+      <c r="AK84" s="9">
+        <f t="shared" si="36"/>
+        <v>33.040000000000006</v>
+      </c>
+      <c r="AL84" s="9">
+        <f t="shared" si="37"/>
+        <v>14.000000000000002</v>
+      </c>
       <c r="AM84" s="9"/>
       <c r="AN84" s="9"/>
       <c r="AO84" s="9"/>
@@ -16769,11 +17001,11 @@
         <v>591</v>
       </c>
       <c r="L85" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-91</v>
       </c>
       <c r="M85" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>500</v>
       </c>
       <c r="N85" s="9"/>
@@ -16784,32 +17016,32 @@
         <v>291</v>
       </c>
       <c r="Q85" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>100</v>
       </c>
       <c r="R85" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>658</v>
       </c>
       <c r="S85" s="4">
+        <f t="shared" si="32"/>
+        <v>658</v>
+      </c>
+      <c r="T85" s="4">
+        <f t="shared" si="33"/>
+        <v>329</v>
+      </c>
+      <c r="U85" s="4">
+        <f t="shared" si="40"/>
+        <v>329</v>
+      </c>
+      <c r="V85" s="9"/>
+      <c r="W85" s="9">
+        <f t="shared" si="34"/>
+        <v>15</v>
+      </c>
+      <c r="X85" s="9">
         <f t="shared" si="31"/>
-        <v>658</v>
-      </c>
-      <c r="T85" s="4">
-        <f t="shared" si="32"/>
-        <v>329</v>
-      </c>
-      <c r="U85" s="4">
-        <f t="shared" si="38"/>
-        <v>329</v>
-      </c>
-      <c r="V85" s="22"/>
-      <c r="W85" s="9">
-        <f t="shared" si="33"/>
-        <v>15</v>
-      </c>
-      <c r="X85" s="9">
-        <f t="shared" si="30"/>
         <v>8.42</v>
       </c>
       <c r="Y85" s="9">
@@ -16844,14 +17076,17 @@
       </c>
       <c r="AI85" s="9"/>
       <c r="AJ85" s="9">
-        <f t="shared" si="34"/>
-        <v>131.6</v>
-      </c>
-      <c r="AK85" s="9">
         <f t="shared" si="35"/>
         <v>131.6</v>
       </c>
-      <c r="AL85" s="9"/>
+      <c r="AK85" s="9">
+        <f t="shared" si="36"/>
+        <v>131.6</v>
+      </c>
+      <c r="AL85" s="9">
+        <f t="shared" si="37"/>
+        <v>40</v>
+      </c>
       <c r="AM85" s="9"/>
       <c r="AN85" s="9"/>
       <c r="AO85" s="9"/>
@@ -16893,11 +17128,11 @@
         <v>61.095999999999997</v>
       </c>
       <c r="L86" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M86" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N86" s="15">
@@ -16908,26 +17143,26 @@
       </c>
       <c r="P86" s="15"/>
       <c r="Q86" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R86" s="18"/>
       <c r="S86" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T86" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U86" s="4"/>
+      <c r="V86" s="9"/>
+      <c r="W86" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X86" s="15" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T86" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U86" s="4"/>
-      <c r="V86" s="22"/>
-      <c r="W86" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X86" s="15" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y86" s="15">
@@ -16962,14 +17197,17 @@
       </c>
       <c r="AI86" s="15"/>
       <c r="AJ86" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK86" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL86" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL86" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM86" s="9"/>
       <c r="AN86" s="9"/>
       <c r="AO86" s="9"/>
@@ -17013,11 +17251,11 @@
         <v>5</v>
       </c>
       <c r="L87" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-5</v>
       </c>
       <c r="M87" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N87" s="15"/>
@@ -17026,26 +17264,26 @@
       </c>
       <c r="P87" s="15"/>
       <c r="Q87" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R87" s="18"/>
       <c r="S87" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T87" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="4"/>
+      <c r="V87" s="9"/>
+      <c r="W87" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X87" s="15" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T87" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U87" s="4"/>
-      <c r="V87" s="22"/>
-      <c r="W87" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X87" s="15" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y87" s="15">
@@ -17082,14 +17320,17 @@
         <v>74</v>
       </c>
       <c r="AJ87" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK87" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL87" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL87" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM87" s="9"/>
       <c r="AN87" s="9"/>
       <c r="AO87" s="9"/>
@@ -17137,11 +17378,11 @@
         <v>186.98</v>
       </c>
       <c r="L88" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-33.336999999999989</v>
       </c>
       <c r="M88" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>153.643</v>
       </c>
       <c r="N88" s="9"/>
@@ -17150,7 +17391,7 @@
       </c>
       <c r="P88" s="9"/>
       <c r="Q88" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>30.7286</v>
       </c>
       <c r="R88" s="4">
@@ -17158,21 +17399,21 @@
         <v>191.11199999999997</v>
       </c>
       <c r="S88" s="4">
-        <f t="shared" si="31"/>
-        <v>191</v>
-      </c>
-      <c r="T88" s="4">
         <f t="shared" si="32"/>
         <v>191</v>
       </c>
+      <c r="T88" s="4">
+        <f t="shared" si="33"/>
+        <v>191</v>
+      </c>
       <c r="U88" s="4"/>
-      <c r="V88" s="22"/>
+      <c r="V88" s="9"/>
       <c r="W88" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>14.996355187024466</v>
       </c>
       <c r="X88" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.7806473448188331</v>
       </c>
       <c r="Y88" s="9">
@@ -17209,14 +17450,17 @@
         <v>37</v>
       </c>
       <c r="AJ88" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>191</v>
       </c>
       <c r="AK88" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL88" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL88" s="9">
+        <f t="shared" si="37"/>
+        <v>30.7286</v>
+      </c>
       <c r="AM88" s="9"/>
       <c r="AN88" s="9"/>
       <c r="AO88" s="9"/>
@@ -17260,11 +17504,11 @@
         <v>10</v>
       </c>
       <c r="L89" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="M89" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>9</v>
       </c>
       <c r="N89" s="15"/>
@@ -17273,26 +17517,26 @@
       </c>
       <c r="P89" s="15"/>
       <c r="Q89" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.8</v>
       </c>
       <c r="R89" s="18"/>
       <c r="S89" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T89" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="4"/>
+      <c r="V89" s="9"/>
+      <c r="W89" s="9">
+        <f t="shared" si="34"/>
+        <v>-5.5555555555555554</v>
+      </c>
+      <c r="X89" s="15">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T89" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U89" s="4"/>
-      <c r="V89" s="22"/>
-      <c r="W89" s="9">
-        <f t="shared" si="33"/>
-        <v>-5.5555555555555554</v>
-      </c>
-      <c r="X89" s="15">
-        <f t="shared" si="30"/>
         <v>-5.5555555555555554</v>
       </c>
       <c r="Y89" s="15">
@@ -17327,14 +17571,17 @@
       </c>
       <c r="AI89" s="15"/>
       <c r="AJ89" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK89" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL89" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL89" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM89" s="9"/>
       <c r="AN89" s="9"/>
       <c r="AO89" s="9"/>
@@ -17376,11 +17623,11 @@
       <c r="J90" s="15"/>
       <c r="K90" s="15"/>
       <c r="L90" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M90" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N90" s="15"/>
@@ -17389,26 +17636,26 @@
       </c>
       <c r="P90" s="15"/>
       <c r="Q90" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R90" s="18"/>
       <c r="S90" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T90" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="4"/>
+      <c r="V90" s="9"/>
+      <c r="W90" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X90" s="15" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T90" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U90" s="4"/>
-      <c r="V90" s="22"/>
-      <c r="W90" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X90" s="15" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y90" s="15">
@@ -17443,14 +17690,17 @@
       </c>
       <c r="AI90" s="15"/>
       <c r="AJ90" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK90" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL90" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL90" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM90" s="9"/>
       <c r="AN90" s="9"/>
       <c r="AO90" s="9"/>
@@ -17496,11 +17746,11 @@
         <v>17</v>
       </c>
       <c r="L91" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M91" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>17</v>
       </c>
       <c r="N91" s="9"/>
@@ -17509,29 +17759,29 @@
       </c>
       <c r="P91" s="9"/>
       <c r="Q91" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.4</v>
       </c>
       <c r="R91" s="4"/>
       <c r="S91" s="4">
-        <f t="shared" ref="S91:S92" si="39">V91</f>
+        <f t="shared" ref="S91:S92" si="41">V91</f>
         <v>40</v>
       </c>
       <c r="T91" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="U91" s="4"/>
-      <c r="V91" s="22">
+      <c r="V91" s="9">
         <f>VLOOKUP(A91,[1]Sheet!$A:$S,19,0)</f>
         <v>40</v>
       </c>
       <c r="W91" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>35.588235294117645</v>
       </c>
       <c r="X91" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>23.823529411764707</v>
       </c>
       <c r="Y91" s="9">
@@ -17568,14 +17818,17 @@
         <v>37</v>
       </c>
       <c r="AJ91" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>13.520000000000001</v>
       </c>
       <c r="AK91" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL91" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL91" s="9">
+        <f t="shared" si="37"/>
+        <v>1.1492</v>
+      </c>
       <c r="AM91" s="9"/>
       <c r="AN91" s="9"/>
       <c r="AO91" s="9"/>
@@ -17621,11 +17874,11 @@
         <v>11</v>
       </c>
       <c r="L92" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M92" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="N92" s="9"/>
@@ -17634,29 +17887,29 @@
       </c>
       <c r="P92" s="9"/>
       <c r="Q92" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="R92" s="4"/>
       <c r="S92" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>40</v>
       </c>
       <c r="T92" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="U92" s="4"/>
-      <c r="V92" s="22">
+      <c r="V92" s="9">
         <f>VLOOKUP(A92,[1]Sheet!$A:$S,19,0)</f>
         <v>40</v>
       </c>
       <c r="W92" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>52.272727272727266</v>
       </c>
       <c r="X92" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>34.090909090909086</v>
       </c>
       <c r="Y92" s="9">
@@ -17693,14 +17946,17 @@
         <v>37</v>
       </c>
       <c r="AJ92" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>13</v>
       </c>
       <c r="AK92" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL92" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL92" s="9">
+        <f t="shared" si="37"/>
+        <v>0.71500000000000008</v>
+      </c>
       <c r="AM92" s="9"/>
       <c r="AN92" s="9"/>
       <c r="AO92" s="9"/>
@@ -17742,11 +17998,11 @@
         <v>16</v>
       </c>
       <c r="L93" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M93" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N93" s="15">
@@ -17757,26 +18013,26 @@
       </c>
       <c r="P93" s="15"/>
       <c r="Q93" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R93" s="18"/>
       <c r="S93" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T93" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="4"/>
+      <c r="V93" s="9"/>
+      <c r="W93" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X93" s="15" t="e">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T93" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U93" s="4"/>
-      <c r="V93" s="22"/>
-      <c r="W93" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X93" s="15" t="e">
-        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y93" s="15">
@@ -17811,14 +18067,17 @@
       </c>
       <c r="AI93" s="15"/>
       <c r="AJ93" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK93" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL93" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL93" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM93" s="9"/>
       <c r="AN93" s="9"/>
       <c r="AO93" s="9"/>
@@ -17866,11 +18125,11 @@
         <v>360</v>
       </c>
       <c r="L94" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-110</v>
       </c>
       <c r="M94" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>234</v>
       </c>
       <c r="N94" s="9">
@@ -17883,32 +18142,32 @@
         <v>198</v>
       </c>
       <c r="Q94" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>46.8</v>
       </c>
       <c r="R94" s="4">
-        <f t="shared" ref="R94:R103" si="40">15*Q94-P94-O94-F94</f>
+        <f t="shared" ref="R94:R103" si="42">15*Q94-P94-O94-F94</f>
         <v>326</v>
       </c>
       <c r="S94" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>326</v>
       </c>
       <c r="T94" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>163</v>
       </c>
       <c r="U94" s="4">
         <f>ROUND(S94*$U$1,0)</f>
         <v>163</v>
       </c>
-      <c r="V94" s="22"/>
+      <c r="V94" s="9"/>
       <c r="W94" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15.000000000000002</v>
       </c>
       <c r="X94" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.0341880341880341</v>
       </c>
       <c r="Y94" s="9">
@@ -17943,14 +18202,17 @@
       </c>
       <c r="AI94" s="9"/>
       <c r="AJ94" s="9">
-        <f t="shared" si="34"/>
-        <v>19.559999999999999</v>
-      </c>
-      <c r="AK94" s="9">
         <f t="shared" si="35"/>
         <v>19.559999999999999</v>
       </c>
-      <c r="AL94" s="9"/>
+      <c r="AK94" s="9">
+        <f t="shared" si="36"/>
+        <v>19.559999999999999</v>
+      </c>
+      <c r="AL94" s="9">
+        <f t="shared" si="37"/>
+        <v>5.6159999999999997</v>
+      </c>
       <c r="AM94" s="9"/>
       <c r="AN94" s="9"/>
       <c r="AO94" s="9"/>
@@ -17996,11 +18258,11 @@
         <v>7</v>
       </c>
       <c r="L95" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M95" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7</v>
       </c>
       <c r="N95" s="9"/>
@@ -18009,26 +18271,26 @@
       </c>
       <c r="P95" s="9"/>
       <c r="Q95" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.4</v>
       </c>
       <c r="R95" s="4"/>
       <c r="S95" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T95" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="4"/>
+      <c r="V95" s="9"/>
+      <c r="W95" s="9">
+        <f t="shared" si="34"/>
+        <v>42.142857142857146</v>
+      </c>
+      <c r="X95" s="9">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T95" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U95" s="4"/>
-      <c r="V95" s="22"/>
-      <c r="W95" s="9">
-        <f t="shared" si="33"/>
-        <v>42.142857142857146</v>
-      </c>
-      <c r="X95" s="9">
-        <f t="shared" si="30"/>
         <v>42.142857142857146</v>
       </c>
       <c r="Y95" s="9">
@@ -18065,14 +18327,17 @@
         <v>37</v>
       </c>
       <c r="AJ95" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK95" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL95" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL95" s="9">
+        <f t="shared" si="37"/>
+        <v>0.21</v>
+      </c>
       <c r="AM95" s="9"/>
       <c r="AN95" s="9"/>
       <c r="AO95" s="9"/>
@@ -18118,11 +18383,11 @@
         <v>5</v>
       </c>
       <c r="L96" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M96" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="N96" s="9"/>
@@ -18131,26 +18396,26 @@
       </c>
       <c r="P96" s="9"/>
       <c r="Q96" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="R96" s="4"/>
       <c r="S96" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T96" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U96" s="4"/>
+      <c r="V96" s="9"/>
+      <c r="W96" s="9">
+        <f t="shared" si="34"/>
+        <v>61</v>
+      </c>
+      <c r="X96" s="9">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T96" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U96" s="4"/>
-      <c r="V96" s="22"/>
-      <c r="W96" s="9">
-        <f t="shared" si="33"/>
-        <v>61</v>
-      </c>
-      <c r="X96" s="9">
-        <f t="shared" si="30"/>
         <v>61</v>
       </c>
       <c r="Y96" s="9">
@@ -18187,14 +18452,17 @@
         <v>37</v>
       </c>
       <c r="AJ96" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK96" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL96" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL96" s="9">
+        <f t="shared" si="37"/>
+        <v>0.15</v>
+      </c>
       <c r="AM96" s="9"/>
       <c r="AN96" s="9"/>
       <c r="AO96" s="9"/>
@@ -18242,11 +18510,11 @@
         <v>388</v>
       </c>
       <c r="L97" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-125</v>
       </c>
       <c r="M97" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>263</v>
       </c>
       <c r="N97" s="9"/>
@@ -18257,32 +18525,32 @@
         <v>267</v>
       </c>
       <c r="Q97" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>52.6</v>
       </c>
       <c r="R97" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>264</v>
       </c>
       <c r="S97" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>264</v>
       </c>
       <c r="T97" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>132</v>
       </c>
       <c r="U97" s="4">
         <f>ROUND(S97*$U$1,0)</f>
         <v>132</v>
       </c>
-      <c r="V97" s="22"/>
+      <c r="V97" s="9"/>
       <c r="W97" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X97" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.9809885931558942</v>
       </c>
       <c r="Y97" s="9">
@@ -18317,14 +18585,17 @@
       </c>
       <c r="AI97" s="9"/>
       <c r="AJ97" s="9">
-        <f t="shared" si="34"/>
-        <v>43.56</v>
-      </c>
-      <c r="AK97" s="9">
         <f t="shared" si="35"/>
         <v>43.56</v>
       </c>
-      <c r="AL97" s="9"/>
+      <c r="AK97" s="9">
+        <f t="shared" si="36"/>
+        <v>43.56</v>
+      </c>
+      <c r="AL97" s="9">
+        <f t="shared" si="37"/>
+        <v>17.358000000000001</v>
+      </c>
       <c r="AM97" s="9"/>
       <c r="AN97" s="9"/>
       <c r="AO97" s="9"/>
@@ -18372,11 +18643,11 @@
         <v>307</v>
       </c>
       <c r="L98" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-135</v>
       </c>
       <c r="M98" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>172</v>
       </c>
       <c r="N98" s="9"/>
@@ -18387,29 +18658,29 @@
         <v>222</v>
       </c>
       <c r="Q98" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>34.4</v>
       </c>
       <c r="R98" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>107</v>
       </c>
       <c r="S98" s="4">
-        <f t="shared" si="31"/>
-        <v>107</v>
-      </c>
-      <c r="T98" s="4">
         <f t="shared" si="32"/>
         <v>107</v>
       </c>
+      <c r="T98" s="4">
+        <f t="shared" si="33"/>
+        <v>107</v>
+      </c>
       <c r="U98" s="4"/>
-      <c r="V98" s="22"/>
+      <c r="V98" s="9"/>
       <c r="W98" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X98" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>11.88953488372093</v>
       </c>
       <c r="Y98" s="9">
@@ -18446,14 +18717,17 @@
         <v>37</v>
       </c>
       <c r="AJ98" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>16.05</v>
       </c>
       <c r="AK98" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL98" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL98" s="9">
+        <f t="shared" si="37"/>
+        <v>5.1599999999999993</v>
+      </c>
       <c r="AM98" s="9"/>
       <c r="AN98" s="9"/>
       <c r="AO98" s="9"/>
@@ -18501,11 +18775,11 @@
         <v>54</v>
       </c>
       <c r="L99" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-11</v>
       </c>
       <c r="M99" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>43</v>
       </c>
       <c r="N99" s="9"/>
@@ -18514,29 +18788,29 @@
       </c>
       <c r="P99" s="9"/>
       <c r="Q99" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.6</v>
       </c>
       <c r="R99" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="S99" s="4">
-        <f t="shared" si="31"/>
-        <v>17</v>
-      </c>
-      <c r="T99" s="4">
         <f t="shared" si="32"/>
         <v>17</v>
       </c>
+      <c r="T99" s="4">
+        <f t="shared" si="33"/>
+        <v>17</v>
+      </c>
       <c r="U99" s="4"/>
-      <c r="V99" s="22"/>
+      <c r="V99" s="9"/>
       <c r="W99" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X99" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>13.023255813953488</v>
       </c>
       <c r="Y99" s="9">
@@ -18573,14 +18847,17 @@
         <v>37</v>
       </c>
       <c r="AJ99" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4.42</v>
       </c>
       <c r="AK99" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL99" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL99" s="9">
+        <f t="shared" si="37"/>
+        <v>2.2359999999999998</v>
+      </c>
       <c r="AM99" s="9"/>
       <c r="AN99" s="9"/>
       <c r="AO99" s="9"/>
@@ -18628,11 +18905,11 @@
         <v>15.4</v>
       </c>
       <c r="L100" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-3.7859999999999996</v>
       </c>
       <c r="M100" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>11.614000000000001</v>
       </c>
       <c r="N100" s="9"/>
@@ -18641,26 +18918,26 @@
       </c>
       <c r="P100" s="9"/>
       <c r="Q100" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.3228</v>
       </c>
       <c r="R100" s="4"/>
       <c r="S100" s="4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T100" s="4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="4"/>
+      <c r="V100" s="9"/>
+      <c r="W100" s="9">
+        <f t="shared" si="34"/>
+        <v>44.535904942311006</v>
+      </c>
+      <c r="X100" s="9">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T100" s="4">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U100" s="4"/>
-      <c r="V100" s="22"/>
-      <c r="W100" s="9">
-        <f t="shared" si="33"/>
-        <v>44.535904942311006</v>
-      </c>
-      <c r="X100" s="9">
-        <f t="shared" si="30"/>
         <v>44.535904942311006</v>
       </c>
       <c r="Y100" s="9">
@@ -18697,14 +18974,17 @@
         <v>37</v>
       </c>
       <c r="AJ100" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK100" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL100" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL100" s="9">
+        <f t="shared" si="37"/>
+        <v>2.3228</v>
+      </c>
       <c r="AM100" s="9"/>
       <c r="AN100" s="9"/>
       <c r="AO100" s="9"/>
@@ -18752,11 +19032,11 @@
         <v>72</v>
       </c>
       <c r="L101" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-39</v>
       </c>
       <c r="M101" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>33</v>
       </c>
       <c r="N101" s="9"/>
@@ -18765,7 +19045,7 @@
       </c>
       <c r="P101" s="9"/>
       <c r="Q101" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.6</v>
       </c>
       <c r="R101" s="4"/>
@@ -18774,20 +19054,20 @@
         <v>30</v>
       </c>
       <c r="T101" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>30</v>
       </c>
       <c r="U101" s="4"/>
-      <c r="V101" s="22">
+      <c r="V101" s="9">
         <f>VLOOKUP(A101,[1]Sheet!$A:$S,19,0)</f>
         <v>30</v>
       </c>
       <c r="W101" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>22.878787878787879</v>
       </c>
       <c r="X101" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>18.333333333333336</v>
       </c>
       <c r="Y101" s="9">
@@ -18824,14 +19104,17 @@
         <v>37</v>
       </c>
       <c r="AJ101" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="AK101" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL101" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL101" s="9">
+        <f t="shared" si="37"/>
+        <v>2.0459999999999998</v>
+      </c>
       <c r="AM101" s="9"/>
       <c r="AN101" s="9"/>
       <c r="AO101" s="9"/>
@@ -18879,11 +19162,11 @@
         <v>6</v>
       </c>
       <c r="L102" s="9">
-        <f t="shared" ref="L102:L117" si="41">E102-K102</f>
+        <f t="shared" ref="L102:L117" si="43">E102-K102</f>
         <v>-0.77700000000000014</v>
       </c>
       <c r="M102" s="9">
-        <f t="shared" ref="M102:M117" si="42">E102-N102</f>
+        <f t="shared" ref="M102:M117" si="44">E102-N102</f>
         <v>5.2229999999999999</v>
       </c>
       <c r="N102" s="9"/>
@@ -18892,26 +19175,26 @@
       </c>
       <c r="P102" s="9"/>
       <c r="Q102" s="9">
-        <f t="shared" ref="Q102:Q117" si="43">M102/5</f>
+        <f t="shared" ref="Q102:Q117" si="45">M102/5</f>
         <v>1.0446</v>
       </c>
       <c r="R102" s="4"/>
       <c r="S102" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T102" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U102" s="4"/>
-      <c r="V102" s="22"/>
+      <c r="V102" s="9"/>
       <c r="W102" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>84.98946965345587</v>
       </c>
       <c r="X102" s="9">
-        <f t="shared" ref="X102:X117" si="44">(F102+O102+P102)/Q102</f>
+        <f t="shared" ref="X102:X117" si="46">(F102+O102+P102)/Q102</f>
         <v>84.98946965345587</v>
       </c>
       <c r="Y102" s="9">
@@ -18948,14 +19231,17 @@
         <v>37</v>
       </c>
       <c r="AJ102" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK102" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL102" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL102" s="9">
+        <f t="shared" si="37"/>
+        <v>1.0446</v>
+      </c>
       <c r="AM102" s="9"/>
       <c r="AN102" s="9"/>
       <c r="AO102" s="9"/>
@@ -19003,11 +19289,11 @@
         <v>248</v>
       </c>
       <c r="L103" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-12</v>
       </c>
       <c r="M103" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>188</v>
       </c>
       <c r="N103" s="9">
@@ -19018,32 +19304,32 @@
       </c>
       <c r="P103" s="9"/>
       <c r="Q103" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>37.6</v>
       </c>
       <c r="R103" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>284</v>
       </c>
       <c r="S103" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>284</v>
       </c>
       <c r="T103" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>142</v>
       </c>
       <c r="U103" s="4">
         <f>ROUND(S103*$U$1,0)</f>
         <v>142</v>
       </c>
-      <c r="V103" s="22"/>
+      <c r="V103" s="9"/>
       <c r="W103" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X103" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>7.4468085106382977</v>
       </c>
       <c r="Y103" s="9">
@@ -19078,14 +19364,17 @@
       </c>
       <c r="AI103" s="9"/>
       <c r="AJ103" s="9">
-        <f t="shared" si="34"/>
-        <v>56.800000000000004</v>
-      </c>
-      <c r="AK103" s="9">
         <f t="shared" si="35"/>
         <v>56.800000000000004</v>
       </c>
-      <c r="AL103" s="9"/>
+      <c r="AK103" s="9">
+        <f t="shared" si="36"/>
+        <v>56.800000000000004</v>
+      </c>
+      <c r="AL103" s="9">
+        <f t="shared" si="37"/>
+        <v>15.040000000000001</v>
+      </c>
       <c r="AM103" s="9"/>
       <c r="AN103" s="9"/>
       <c r="AO103" s="9"/>
@@ -19127,11 +19416,11 @@
         <v>5.2</v>
       </c>
       <c r="L104" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-5.2</v>
       </c>
       <c r="M104" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N104" s="10"/>
@@ -19140,26 +19429,26 @@
       </c>
       <c r="P104" s="10"/>
       <c r="Q104" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R104" s="12"/>
       <c r="S104" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T104" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U104" s="4"/>
-      <c r="V104" s="22"/>
+      <c r="V104" s="9"/>
       <c r="W104" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X104" s="10" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y104" s="10">
@@ -19196,14 +19485,17 @@
         <v>1001010017536</v>
       </c>
       <c r="AJ104" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK104" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL104" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL104" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM104" s="9"/>
       <c r="AN104" s="9"/>
       <c r="AO104" s="9"/>
@@ -19251,11 +19543,11 @@
         <v>148</v>
       </c>
       <c r="L105" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-90</v>
       </c>
       <c r="M105" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>58</v>
       </c>
       <c r="N105" s="9"/>
@@ -19266,26 +19558,26 @@
         <v>138</v>
       </c>
       <c r="Q105" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>11.6</v>
       </c>
       <c r="R105" s="4"/>
       <c r="S105" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T105" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U105" s="4"/>
-      <c r="V105" s="22"/>
+      <c r="V105" s="9"/>
       <c r="W105" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>18.620689655172413</v>
       </c>
       <c r="X105" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>18.620689655172413</v>
       </c>
       <c r="Y105" s="9">
@@ -19322,14 +19614,17 @@
         <v>154</v>
       </c>
       <c r="AJ105" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK105" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL105" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL105" s="9">
+        <f t="shared" si="37"/>
+        <v>4.0599999999999996</v>
+      </c>
       <c r="AM105" s="9"/>
       <c r="AN105" s="9"/>
       <c r="AO105" s="9"/>
@@ -19377,11 +19672,11 @@
         <v>30.28</v>
       </c>
       <c r="L106" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-1.4879999999999995</v>
       </c>
       <c r="M106" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>28.792000000000002</v>
       </c>
       <c r="N106" s="9"/>
@@ -19390,26 +19685,26 @@
       </c>
       <c r="P106" s="9"/>
       <c r="Q106" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>5.7584</v>
       </c>
       <c r="R106" s="4"/>
       <c r="S106" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T106" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U106" s="4"/>
-      <c r="V106" s="22"/>
+      <c r="V106" s="9"/>
       <c r="W106" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>28.698423173103642</v>
       </c>
       <c r="X106" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>28.698423173103642</v>
       </c>
       <c r="Y106" s="9">
@@ -19446,14 +19741,17 @@
         <v>75</v>
       </c>
       <c r="AJ106" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK106" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL106" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL106" s="9">
+        <f t="shared" si="37"/>
+        <v>5.7584</v>
+      </c>
       <c r="AM106" s="9"/>
       <c r="AN106" s="9"/>
       <c r="AO106" s="9"/>
@@ -19499,11 +19797,11 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="L107" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>9.9999999999999645E-2</v>
       </c>
       <c r="M107" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>8.4</v>
       </c>
       <c r="N107" s="9"/>
@@ -19512,7 +19810,7 @@
       </c>
       <c r="P107" s="9"/>
       <c r="Q107" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>1.6800000000000002</v>
       </c>
       <c r="R107" s="4">
@@ -19520,21 +19818,21 @@
         <v>5.2390000000000025</v>
       </c>
       <c r="S107" s="4">
-        <f t="shared" si="31"/>
-        <v>5</v>
-      </c>
-      <c r="T107" s="4">
         <f t="shared" si="32"/>
         <v>5</v>
       </c>
+      <c r="T107" s="4">
+        <f t="shared" si="33"/>
+        <v>5</v>
+      </c>
       <c r="U107" s="4"/>
-      <c r="V107" s="22"/>
+      <c r="V107" s="9"/>
       <c r="W107" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>14.857738095238092</v>
       </c>
       <c r="X107" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>11.881547619047618</v>
       </c>
       <c r="Y107" s="9">
@@ -19569,14 +19867,17 @@
       </c>
       <c r="AI107" s="9"/>
       <c r="AJ107" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5</v>
       </c>
       <c r="AK107" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL107" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL107" s="9">
+        <f t="shared" si="37"/>
+        <v>1.6800000000000002</v>
+      </c>
       <c r="AM107" s="9"/>
       <c r="AN107" s="9"/>
       <c r="AO107" s="9"/>
@@ -19624,11 +19925,11 @@
         <v>252</v>
       </c>
       <c r="L108" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-15</v>
       </c>
       <c r="M108" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>181</v>
       </c>
       <c r="N108" s="9">
@@ -19639,7 +19940,7 @@
       </c>
       <c r="P108" s="9"/>
       <c r="Q108" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>36.200000000000003</v>
       </c>
       <c r="R108" s="4">
@@ -19647,24 +19948,24 @@
         <v>329.6</v>
       </c>
       <c r="S108" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>330</v>
       </c>
       <c r="T108" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>165</v>
       </c>
       <c r="U108" s="4">
         <f>ROUND(S108*$U$1,0)</f>
         <v>165</v>
       </c>
-      <c r="V108" s="22"/>
+      <c r="V108" s="9"/>
       <c r="W108" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>13.011049723756905</v>
       </c>
       <c r="X108" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>3.895027624309392</v>
       </c>
       <c r="Y108" s="9">
@@ -19701,14 +20002,17 @@
         <v>158</v>
       </c>
       <c r="AJ108" s="9">
-        <f t="shared" si="34"/>
-        <v>54.45</v>
-      </c>
-      <c r="AK108" s="9">
         <f t="shared" si="35"/>
         <v>54.45</v>
       </c>
-      <c r="AL108" s="9"/>
+      <c r="AK108" s="9">
+        <f t="shared" si="36"/>
+        <v>54.45</v>
+      </c>
+      <c r="AL108" s="9">
+        <f t="shared" si="37"/>
+        <v>11.946000000000002</v>
+      </c>
       <c r="AM108" s="9"/>
       <c r="AN108" s="9"/>
       <c r="AO108" s="9"/>
@@ -19756,11 +20060,11 @@
         <v>30</v>
       </c>
       <c r="L109" s="15">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-21</v>
       </c>
       <c r="M109" s="15">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>9</v>
       </c>
       <c r="N109" s="15"/>
@@ -19769,26 +20073,26 @@
       </c>
       <c r="P109" s="15"/>
       <c r="Q109" s="15">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>1.8</v>
       </c>
       <c r="R109" s="18"/>
       <c r="S109" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T109" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U109" s="4"/>
-      <c r="V109" s="22"/>
+      <c r="V109" s="9"/>
       <c r="W109" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-1.1111111111111112</v>
       </c>
       <c r="X109" s="15">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-1.1111111111111112</v>
       </c>
       <c r="Y109" s="15">
@@ -19825,14 +20129,17 @@
         <v>160</v>
       </c>
       <c r="AJ109" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK109" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL109" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL109" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM109" s="9"/>
       <c r="AN109" s="9"/>
       <c r="AO109" s="9"/>
@@ -19880,11 +20187,11 @@
         <v>252</v>
       </c>
       <c r="L110" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-80</v>
       </c>
       <c r="M110" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>132</v>
       </c>
       <c r="N110" s="9">
@@ -19897,26 +20204,26 @@
         <v>132</v>
       </c>
       <c r="Q110" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>26.4</v>
       </c>
       <c r="R110" s="4"/>
       <c r="S110" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T110" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U110" s="4"/>
-      <c r="V110" s="22"/>
+      <c r="V110" s="9"/>
       <c r="W110" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>16.401515151515152</v>
       </c>
       <c r="X110" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>16.401515151515152</v>
       </c>
       <c r="Y110" s="9">
@@ -19953,14 +20260,17 @@
         <v>162</v>
       </c>
       <c r="AJ110" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK110" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL110" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL110" s="9">
+        <f t="shared" si="37"/>
+        <v>2.64</v>
+      </c>
       <c r="AM110" s="9"/>
       <c r="AN110" s="9"/>
       <c r="AO110" s="9"/>
@@ -20008,11 +20318,11 @@
         <v>460</v>
       </c>
       <c r="L111" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-99</v>
       </c>
       <c r="M111" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>321</v>
       </c>
       <c r="N111" s="9">
@@ -20025,7 +20335,7 @@
         <v>138</v>
       </c>
       <c r="Q111" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>64.2</v>
       </c>
       <c r="R111" s="4">
@@ -20033,24 +20343,24 @@
         <v>356</v>
       </c>
       <c r="S111" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>356</v>
       </c>
       <c r="T111" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>178</v>
       </c>
       <c r="U111" s="4">
         <f>ROUND(S111*$U$1,0)</f>
         <v>178</v>
       </c>
-      <c r="V111" s="22"/>
+      <c r="V111" s="9"/>
       <c r="W111" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X111" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>9.4548286604361369</v>
       </c>
       <c r="Y111" s="9">
@@ -20087,14 +20397,17 @@
         <v>164</v>
       </c>
       <c r="AJ111" s="9">
-        <f t="shared" si="34"/>
-        <v>17.8</v>
-      </c>
-      <c r="AK111" s="9">
         <f t="shared" si="35"/>
         <v>17.8</v>
       </c>
-      <c r="AL111" s="9"/>
+      <c r="AK111" s="9">
+        <f t="shared" si="36"/>
+        <v>17.8</v>
+      </c>
+      <c r="AL111" s="9">
+        <f t="shared" si="37"/>
+        <v>6.4200000000000008</v>
+      </c>
       <c r="AM111" s="9"/>
       <c r="AN111" s="9"/>
       <c r="AO111" s="9"/>
@@ -20138,11 +20451,11 @@
         <v>34</v>
       </c>
       <c r="L112" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-34</v>
       </c>
       <c r="M112" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N112" s="10"/>
@@ -20151,26 +20464,26 @@
       </c>
       <c r="P112" s="10"/>
       <c r="Q112" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R112" s="12"/>
       <c r="S112" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T112" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U112" s="4"/>
-      <c r="V112" s="22"/>
+      <c r="V112" s="9"/>
       <c r="W112" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X112" s="10" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y112" s="10">
@@ -20207,14 +20520,17 @@
         <v>1001066607626</v>
       </c>
       <c r="AJ112" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK112" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL112" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL112" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM112" s="9"/>
       <c r="AN112" s="9"/>
       <c r="AO112" s="9"/>
@@ -20262,11 +20578,11 @@
         <v>658</v>
       </c>
       <c r="L113" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-112</v>
       </c>
       <c r="M113" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>506</v>
       </c>
       <c r="N113" s="9">
@@ -20279,7 +20595,7 @@
         <v>330</v>
       </c>
       <c r="Q113" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>101.2</v>
       </c>
       <c r="R113" s="4">
@@ -20287,24 +20603,24 @@
         <v>605</v>
       </c>
       <c r="S113" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>605</v>
       </c>
       <c r="T113" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>302</v>
       </c>
       <c r="U113" s="4">
         <f>ROUND(S113*$U$1,0)</f>
         <v>303</v>
       </c>
-      <c r="V113" s="22"/>
+      <c r="V113" s="9"/>
       <c r="W113" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15</v>
       </c>
       <c r="X113" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>9.0217391304347831</v>
       </c>
       <c r="Y113" s="9">
@@ -20341,14 +20657,17 @@
         <v>167</v>
       </c>
       <c r="AJ113" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>120.80000000000001</v>
       </c>
       <c r="AK113" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>121.2</v>
       </c>
-      <c r="AL113" s="9"/>
+      <c r="AL113" s="9">
+        <f t="shared" si="37"/>
+        <v>40.480000000000004</v>
+      </c>
       <c r="AM113" s="9"/>
       <c r="AN113" s="9"/>
       <c r="AO113" s="9"/>
@@ -20394,11 +20713,11 @@
         <v>4</v>
       </c>
       <c r="L114" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-6</v>
       </c>
       <c r="M114" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>-2</v>
       </c>
       <c r="N114" s="9"/>
@@ -20407,26 +20726,26 @@
       </c>
       <c r="P114" s="9"/>
       <c r="Q114" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-0.4</v>
       </c>
       <c r="R114" s="4"/>
       <c r="S114" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T114" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U114" s="4"/>
-      <c r="V114" s="22"/>
+      <c r="V114" s="9"/>
       <c r="W114" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-425</v>
       </c>
       <c r="X114" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>-425</v>
       </c>
       <c r="Y114" s="9">
@@ -20463,14 +20782,17 @@
         <v>75</v>
       </c>
       <c r="AJ114" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK114" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL114" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL114" s="9">
+        <f t="shared" si="37"/>
+        <v>-4.0000000000000008E-2</v>
+      </c>
       <c r="AM114" s="9"/>
       <c r="AN114" s="9"/>
       <c r="AO114" s="9"/>
@@ -20516,11 +20838,11 @@
         <v>6</v>
       </c>
       <c r="L115" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-4</v>
       </c>
       <c r="M115" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>2</v>
       </c>
       <c r="N115" s="9"/>
@@ -20529,26 +20851,26 @@
       </c>
       <c r="P115" s="9"/>
       <c r="Q115" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.4</v>
       </c>
       <c r="R115" s="4"/>
       <c r="S115" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T115" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U115" s="4"/>
-      <c r="V115" s="22"/>
+      <c r="V115" s="9"/>
       <c r="W115" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>377.5</v>
       </c>
       <c r="X115" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>377.5</v>
       </c>
       <c r="Y115" s="9">
@@ -20585,14 +20907,17 @@
         <v>75</v>
       </c>
       <c r="AJ115" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK115" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL115" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL115" s="9">
+        <f t="shared" si="37"/>
+        <v>4.0000000000000008E-2</v>
+      </c>
       <c r="AM115" s="9"/>
       <c r="AN115" s="9"/>
       <c r="AO115" s="9"/>
@@ -20638,11 +20963,11 @@
         <v>16</v>
       </c>
       <c r="L116" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-1</v>
       </c>
       <c r="M116" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>15</v>
       </c>
       <c r="N116" s="9"/>
@@ -20651,7 +20976,7 @@
       </c>
       <c r="P116" s="9"/>
       <c r="Q116" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>3</v>
       </c>
       <c r="R116" s="4"/>
@@ -20660,20 +20985,20 @@
         <v>40</v>
       </c>
       <c r="T116" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="U116" s="4"/>
-      <c r="V116" s="22">
+      <c r="V116" s="9">
         <f>VLOOKUP(A116,[1]Sheet!$A:$S,19,0)</f>
         <v>40</v>
       </c>
       <c r="W116" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>48.333333333333336</v>
       </c>
       <c r="X116" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>35</v>
       </c>
       <c r="Y116" s="9">
@@ -20710,14 +21035,17 @@
         <v>37</v>
       </c>
       <c r="AJ116" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>12</v>
       </c>
       <c r="AK116" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL116" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL116" s="9">
+        <f t="shared" si="37"/>
+        <v>0.89999999999999991</v>
+      </c>
       <c r="AM116" s="9"/>
       <c r="AN116" s="9"/>
       <c r="AO116" s="9"/>
@@ -20753,11 +21081,11 @@
       <c r="J117" s="9"/>
       <c r="K117" s="9"/>
       <c r="L117" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M117" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N117" s="9"/>
@@ -20766,26 +21094,26 @@
       </c>
       <c r="P117" s="9"/>
       <c r="Q117" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R117" s="4"/>
       <c r="S117" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="T117" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U117" s="4"/>
-      <c r="V117" s="22"/>
+      <c r="V117" s="9"/>
       <c r="W117" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X117" s="9" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y117" s="9">
@@ -20822,14 +21150,17 @@
         <v>172</v>
       </c>
       <c r="AJ117" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK117" s="9">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="AL117" s="9"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL117" s="9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AM117" s="9"/>
       <c r="AN117" s="9"/>
       <c r="AO117" s="9"/>
